--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,419 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E8" s="3">
         <v>120900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>142800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>149500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>139400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>140700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>166600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>168000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>178200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>184400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>169300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>145700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>130300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>123600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>105100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>95000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>96300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>114000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>121100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>114900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>128400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>131200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>118200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>104800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>131900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>167400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>161800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E9" s="3">
         <v>96200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>104700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>111000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>109700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>97100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>108500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>113400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>121300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>111800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>105100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>94600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>90200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>87600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>80400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>75100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>74000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>81400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>87300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>86900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>91800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>95300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>85100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>74600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>96900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>111600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>108400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E10" s="3">
         <v>24700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>38100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>39500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>38900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>43600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>58100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>63400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>64800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>78800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>72600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>64200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>51100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>40100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>36000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>32600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>33800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>28000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>36600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>35900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>33100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>30200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>35000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>55800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>53400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1101,8 +1113,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1193,8 +1206,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1285,8 +1301,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1377,8 +1396,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1469,8 +1491,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1500,192 +1525,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>120300</v>
+      </c>
+      <c r="E17" s="3">
         <v>114600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>124400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>132400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>129500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>119500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>115500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>127800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>123300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>131500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>140400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>132400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>127200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>112800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>106200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>103500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>95300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>89400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>88900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>97600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>104000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>103000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>109000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>112600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>104400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>91500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>116600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>133500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>130200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E18" s="3">
         <v>6300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>38800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>44700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>59700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>52000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>42100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>18600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>33900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>31600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1718,225 +1750,232 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="E20" s="3">
         <v>1900</v>
       </c>
       <c r="F20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>900</v>
       </c>
       <c r="J20" s="3">
         <v>900</v>
       </c>
       <c r="K20" s="3">
+        <v>900</v>
+      </c>
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>700</v>
       </c>
       <c r="R20" s="3">
         <v>700</v>
       </c>
       <c r="S20" s="3">
+        <v>700</v>
+      </c>
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1000</v>
       </c>
       <c r="V20" s="3">
         <v>1000</v>
       </c>
       <c r="W20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>300</v>
       </c>
       <c r="AD20" s="3">
         <v>300</v>
       </c>
       <c r="AE20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E21" s="3">
         <v>14700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>27400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>50100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>67500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>59900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>48500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>40200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>17800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>15900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>20400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>28200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>27100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>20800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>25000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>43500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>42500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1944,28 +1983,28 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -1976,8 +2015,8 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1994,192 +2033,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>48000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>60300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>52400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>42600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>17400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>12200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>18900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>14300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>13400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>34200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>32400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>11500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2270,192 +2318,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E26" s="3">
         <v>7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>38100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>44400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>38200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>31700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>13000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>14300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>22200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E27" s="3">
         <v>7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>38100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>44400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>38200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>13000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>14300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2546,8 +2603,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2602,8 +2662,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2620,11 +2680,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>500</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2638,8 +2698,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2730,8 +2793,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2822,192 +2888,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="E32" s="3">
         <v>-1900</v>
       </c>
       <c r="F32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-900</v>
       </c>
       <c r="J32" s="3">
         <v>-900</v>
       </c>
       <c r="K32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-700</v>
       </c>
       <c r="R32" s="3">
         <v>-700</v>
       </c>
       <c r="S32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1000</v>
       </c>
       <c r="V32" s="3">
         <v>-1000</v>
       </c>
       <c r="W32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-300</v>
       </c>
       <c r="AD32" s="3">
         <v>-300</v>
       </c>
       <c r="AE32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E33" s="3">
         <v>7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>38100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>44400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>38200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>31700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>13000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>15200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>14300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3098,197 +3173,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E35" s="3">
         <v>7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>38100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>44400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>38200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>31700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>13000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>15200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>14300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3321,8 +3405,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3355,165 +3440,169 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E41" s="3">
         <v>13600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>65200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>38000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>32200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>35400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>137800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>131700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>102700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>63500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>45400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>44000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>35100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>87100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E42" s="3">
         <v>106500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>126200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>122000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>159100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>165300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>165000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>170000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>200000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>165000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>150000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>122000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>121000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>104000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>208900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>149600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>129500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>114500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>99600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>99500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>114300</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
@@ -3530,8 +3619,8 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3539,8 +3628,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3548,367 +3640,379 @@
         <v>59900</v>
       </c>
       <c r="E43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="F43" s="3">
         <v>53100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>65200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>65400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>69300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>57000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>71900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>76100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>73200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>57900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>58200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>53700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>55800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>52600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>56000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>41500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>52200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>45000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>46800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>50100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>61100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>60100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>53200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>55600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>77600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>69400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E44" s="3">
         <v>79300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>69400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>62000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>65000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>61500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>57100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>46900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>43900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>39100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>32000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>28800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>29100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>18300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>28300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>33000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>41500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>36500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>31400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>26200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>24000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>26100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>52200</v>
       </c>
       <c r="AC44" s="3">
         <v>52200</v>
       </c>
       <c r="AD44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AE44" s="3">
         <v>55000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>54500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E45" s="3">
         <v>14800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>271400</v>
+      </c>
+      <c r="E46" s="3">
         <v>274000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>268100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>264000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>361800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>351000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>334100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>336300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>328700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>308900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>285600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>252200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>234400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>213000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>294900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>264600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>249300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>229900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>220500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>226700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>232200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>214400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>208500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>192900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>166800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>153300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>154200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>170900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>214800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3999,100 +4103,106 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>72700</v>
+        <v>74300</v>
       </c>
       <c r="E48" s="3">
         <v>72700</v>
       </c>
       <c r="F48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="G48" s="3">
         <v>75800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>80500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>77700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>80700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>75300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>69500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>70800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>72900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>62700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>67900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>73300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>76500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>72100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>74300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>80700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>82700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>84400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>90000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>97100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>103800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>91600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>96600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>102200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>104200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4183,8 +4293,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4275,8 +4388,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4367,100 +4483,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E52" s="3">
         <v>53700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>56200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>49300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>35800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>44900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>41000</v>
       </c>
       <c r="O52" s="3">
         <v>41000</v>
       </c>
       <c r="P52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Q52" s="3">
         <v>34900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>27000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>23100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>24300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>20600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>13700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>32600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>33300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>31000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>27900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4551,100 +4673,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>398800</v>
+      </c>
+      <c r="E54" s="3">
         <v>400400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>396900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>389100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>484800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>460900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>443700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>446500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>442300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>420100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>398900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>364100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>348300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>310600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>389900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>362400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>349000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>328500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>320900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>331700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>335500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>316100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>312800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>303300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>284300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>277500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>284100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>304100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>346900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4677,8 +4805,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4711,100 +4840,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E57" s="3">
         <v>29100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>38100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>37900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>34500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>28800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>29300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>21900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>27800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>33000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>30200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>28900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>28200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>32400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>30800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>34600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>45300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4895,192 +5028,201 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E59" s="3">
         <v>32000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>128100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>27500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>45100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>36600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>33700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>31900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>38200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>31600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>33500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>35900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>20300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>23500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>21800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>33100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>32400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E60" s="3">
         <v>61200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>163100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>60200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>66200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>77100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>80400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>77700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>73000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>67400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>76300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>62500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>61200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>48700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>55600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>71200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>61800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>62400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>64000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>52700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>54300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>56400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>78400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>80900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5171,8 +5313,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5180,91 +5325,94 @@
         <v>3900</v>
       </c>
       <c r="E62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F62" s="3">
         <v>3800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2300</v>
       </c>
       <c r="J62" s="3">
         <v>2300</v>
       </c>
       <c r="K62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="L62" s="3">
         <v>1600</v>
       </c>
       <c r="M62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2200</v>
-      </c>
-      <c r="W62" s="3">
-        <v>100</v>
       </c>
       <c r="X62" s="3">
         <v>100</v>
       </c>
       <c r="Y62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z62" s="3">
         <v>1000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5355,8 +5503,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5447,8 +5598,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5539,100 +5693,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E66" s="3">
         <v>65000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>67000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>168000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>62400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>56800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>68500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>78700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>79700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>83600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>69300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>78300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>63500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>50900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>57800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>71300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>63300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>64800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>54200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>55000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>56500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>79100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>81000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5665,8 +5825,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5757,8 +5918,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5849,8 +6013,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5941,8 +6108,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6033,100 +6203,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>418100</v>
+      </c>
+      <c r="E72" s="3">
         <v>410900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>409700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>399400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>393100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>471400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>461400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>452900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>438100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>414100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>396800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>367800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>342600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>320900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>392900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>380500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>368200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>362000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>359600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>358600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>350400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>341900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>338800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>329300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>321300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>314700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>309400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>307800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>293400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6217,8 +6393,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6309,8 +6488,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6401,100 +6583,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>331700</v>
+      </c>
+      <c r="E76" s="3">
         <v>335300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>333200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>322100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>316700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>398500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>387000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>378000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>363700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>338100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>319100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>288500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>264700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>241300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>311500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>297800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>285500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>277600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>275800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>273900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>264200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>254200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>249400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>238500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>230100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>222500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>227600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>225000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>265900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6585,197 +6773,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E81" s="3">
         <v>7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>38100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>44400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>38200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>31700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>13000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>15200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>14300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6808,13 +7005,14 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6500</v>
+        <v>2800</v>
       </c>
       <c r="E83" s="3">
         <v>6500</v>
@@ -6823,34 +7021,34 @@
         <v>6500</v>
       </c>
       <c r="G83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H83" s="3">
         <v>5700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>6700</v>
       </c>
       <c r="I83" s="3">
         <v>6700</v>
       </c>
       <c r="J83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K83" s="3">
         <v>6800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>7300</v>
       </c>
       <c r="M83" s="3">
         <v>7300</v>
       </c>
       <c r="N83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="O83" s="3">
         <v>7500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5900</v>
-      </c>
-      <c r="P83" s="3">
-        <v>7200</v>
       </c>
       <c r="Q83" s="3">
         <v>7200</v>
@@ -6859,10 +7057,10 @@
         <v>7200</v>
       </c>
       <c r="S83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="T83" s="3">
         <v>6900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7500</v>
       </c>
       <c r="U83" s="3">
         <v>7500</v>
@@ -6874,7 +7072,7 @@
         <v>7500</v>
       </c>
       <c r="X83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="Y83" s="3">
         <v>8200</v>
@@ -6886,22 +7084,25 @@
         <v>8200</v>
       </c>
       <c r="AB83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AC83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>9300</v>
       </c>
       <c r="AD83" s="3">
         <v>9300</v>
       </c>
       <c r="AE83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AF83" s="3">
         <v>10100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6992,8 +7193,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7084,8 +7288,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7176,8 +7383,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7268,8 +7478,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7360,100 +7573,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>55300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>48400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>61800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>47000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>31100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>40700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>24200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>45300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>42200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>19100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>21000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>18900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>19400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7486,100 +7705,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7670,8 +7893,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7762,100 +7988,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>13000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>35500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-48100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-33900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-61500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>102900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-61100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-24200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>12100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-119900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7888,100 +8120,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-6400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-5700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-95800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-7200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-8300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-12000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-15200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-13900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-17600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-15100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-12500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-9800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-94800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-5100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AE96" s="3">
         <v>-7800</v>
       </c>
       <c r="AF96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8072,8 +8308,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8164,8 +8403,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8256,100 +8498,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-97900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-94800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8440,96 +8688,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-57100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-99300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>29000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>39200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>8900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,431 +656,444 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E8" s="3">
         <v>130600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>120900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>142800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>139400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>140700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>166600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>168000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>178200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>184400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>169300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>145700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>130300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>123600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>105100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>95000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>96300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>114000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>121100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>114900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>128400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>131200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>118200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>104800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>131900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>167400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>161800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E9" s="3">
         <v>98400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>96200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>104700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>111000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>109700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>100500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>97100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>108500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>104600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>113400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>121300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>111800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>105100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>94600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>90200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>87600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>80400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>75100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>74000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>81400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>87300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>86900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>91800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>95300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>85100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>74600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>96900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>111600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>108400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E10" s="3">
         <v>32200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>39500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>43600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>58100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>63400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>64800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>78800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>72600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>64200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>51100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>40100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>36000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>32600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>33800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>28000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>36600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>35900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>33100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>30200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>35000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>55800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>53400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1114,8 +1127,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1209,8 +1223,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1304,8 +1321,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1399,8 +1419,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1494,8 +1517,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1526,198 +1552,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E17" s="3">
         <v>120300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>114600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>124400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>132400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>129500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>119500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>115500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>127800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>123300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>131500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>140400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>127200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>112800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>106200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>103500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>95300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>89400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>88900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>97600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>104000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>103000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>109000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>112600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>104400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>91500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>116600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>133500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>130200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E18" s="3">
         <v>10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>25200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>38800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>44700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>59700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>52000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>18600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>33900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1751,198 +1784,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1900</v>
       </c>
       <c r="F20" s="3">
         <v>1900</v>
       </c>
       <c r="G20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>900</v>
       </c>
       <c r="K20" s="3">
         <v>900</v>
       </c>
       <c r="L20" s="3">
+        <v>900</v>
+      </c>
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>700</v>
       </c>
       <c r="S20" s="3">
         <v>700</v>
       </c>
       <c r="T20" s="3">
+        <v>700</v>
+      </c>
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>900</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1000</v>
       </c>
       <c r="W20" s="3">
         <v>1000</v>
       </c>
       <c r="X20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>300</v>
       </c>
       <c r="AE20" s="3">
         <v>300</v>
       </c>
       <c r="AF20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E21" s="3">
         <v>14800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>50100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>55400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>67500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>59900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>48500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>31900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>15900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>25000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>20400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>22600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>20800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>25000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>43500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>42500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1950,35 +1990,35 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1986,28 +2026,28 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
@@ -2018,8 +2058,8 @@
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2036,198 +2076,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>12000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>26100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>39500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>48000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>60300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>52400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>42600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>32900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>18900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>13400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>15700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>34200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>32400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2321,198 +2370,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E26" s="3">
         <v>10200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>38100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>38200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>13000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>22200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E27" s="3">
         <v>10200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>38100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>44400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>38200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>13000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>14300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>22200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2606,8 +2664,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2665,8 +2726,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2683,11 +2744,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>500</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2701,8 +2762,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2796,8 +2860,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2891,198 +2958,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1900</v>
       </c>
       <c r="F32" s="3">
         <v>-1900</v>
       </c>
       <c r="G32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-900</v>
       </c>
       <c r="K32" s="3">
         <v>-900</v>
       </c>
       <c r="L32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-700</v>
       </c>
       <c r="S32" s="3">
         <v>-700</v>
       </c>
       <c r="T32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-900</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1000</v>
       </c>
       <c r="W32" s="3">
         <v>-1000</v>
       </c>
       <c r="X32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-300</v>
       </c>
       <c r="AE32" s="3">
         <v>-300</v>
       </c>
       <c r="AF32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E33" s="3">
         <v>10200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>38100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>44400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>38200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>13000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>15200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>10300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>22200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3176,203 +3252,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E35" s="3">
         <v>10200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>38100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>44400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>38200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>13000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>15200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>10300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>22200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3406,8 +3491,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3441,171 +3527,175 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E41" s="3">
         <v>15200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>65200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>38000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>35400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>32200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>35400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>137800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>131700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>102700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>63500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>45400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>44000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>35100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>87100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E42" s="3">
         <v>102500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>106500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>126200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>122000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>159100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>165300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>165000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>170000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>200000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>165000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>150000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>122000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>121000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>104000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>208900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>149600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>129500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>114500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>99600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>99500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>114300</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>8</v>
@@ -3622,8 +3712,8 @@
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -3631,388 +3721,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>59900</v>
+        <v>65800</v>
       </c>
       <c r="E43" s="3">
         <v>59900</v>
       </c>
       <c r="F43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="G43" s="3">
         <v>53100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>65200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>65400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>69300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>57000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>76100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>73200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>57900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>53700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>55800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>52600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>56000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>41500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>52200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>45000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>46800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>50100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>61100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>60100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>53200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>55600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>77600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>69400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E44" s="3">
         <v>79800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>79300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>69400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>62000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>65000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>61500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>57100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>46900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>43900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>39100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>32000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>28800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>29100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>18300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>28300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>33000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>41500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>36500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>31400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>26200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>24000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>26100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>52200</v>
       </c>
       <c r="AD44" s="3">
         <v>52200</v>
       </c>
       <c r="AE44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AF44" s="3">
         <v>55000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>54500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E45" s="3">
         <v>14100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E46" s="3">
         <v>271400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>274000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>268100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>264000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>361800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>351000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>334100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>336300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>328700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>308900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>285600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>252200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>234400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>213000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>294900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>264600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>249300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>229900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>220500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>226700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>232200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>214400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>208500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>192900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>166800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>153300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>154200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>170900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>214800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4106,103 +4211,109 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E48" s="3">
         <v>74300</v>
-      </c>
-      <c r="E48" s="3">
-        <v>72700</v>
       </c>
       <c r="F48" s="3">
         <v>72700</v>
       </c>
       <c r="G48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="H48" s="3">
         <v>75800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>80500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>74000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>77700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>80700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>75300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>66300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>69500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>70800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>72900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>62700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>67900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>73300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>76500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>72100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>74300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>80700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>82700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>84400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>90000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>97100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>103800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>91600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>96600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>102200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>104200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4296,8 +4407,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4391,8 +4505,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4486,103 +4603,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E52" s="3">
         <v>53100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>56200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>49300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>44900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>41000</v>
       </c>
       <c r="P52" s="3">
         <v>41000</v>
       </c>
       <c r="Q52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="R52" s="3">
         <v>34900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>27000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>24400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>23100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>13300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>13700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>32600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>33300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>31000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>27900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4676,103 +4799,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>385000</v>
+      </c>
+      <c r="E54" s="3">
         <v>398800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>400400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>396900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>389100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>484800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>460900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>443700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>446500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>442300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>420100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>398900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>364100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>348300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>310600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>389900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>362400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>349000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>328500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>320900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>331700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>335500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>316100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>312800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>303300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>284300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>277500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>284100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>304100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>346900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4806,8 +4935,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4841,103 +4971,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E57" s="3">
         <v>31100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>36200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>38100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>37900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>34500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>39700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>28800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>29300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>21900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>27800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>33000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>30200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>28900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>28200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>32400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>30800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>34600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>45300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>48500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5031,198 +5165,207 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E59" s="3">
         <v>32100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>128100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>32700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>39800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>38500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>45100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>36600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>33700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>31900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>38200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>31600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>35900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>20300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>23500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>21800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>33100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>32400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E60" s="3">
         <v>63200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>59900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>163100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>60200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>54500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>66200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>77100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>80400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>77700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>73000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>81800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>67400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>76300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>62500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>61200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>48700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>55600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>71200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>61800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>62400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>64000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>52700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>54300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>56400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>78400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>80900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5316,103 +5459,109 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3900</v>
+        <v>3000</v>
       </c>
       <c r="E62" s="3">
         <v>3900</v>
       </c>
       <c r="F62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G62" s="3">
         <v>3800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2300</v>
       </c>
       <c r="K62" s="3">
         <v>2300</v>
       </c>
       <c r="L62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="M62" s="3">
         <v>1600</v>
       </c>
       <c r="N62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O62" s="3">
         <v>2000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2200</v>
-      </c>
-      <c r="X62" s="3">
-        <v>100</v>
       </c>
       <c r="Y62" s="3">
         <v>100</v>
       </c>
       <c r="Z62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5506,8 +5655,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5601,8 +5753,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5696,103 +5851,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E66" s="3">
         <v>67100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>65000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>67000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>168000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>62400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>56800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>68500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>82000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>79700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>83600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>69300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>78300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>63500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>50900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>45100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>57800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>71300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>61900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>63300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>64800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>54200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>55000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>56500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>79100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>81000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5826,8 +5987,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5921,8 +6083,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6016,8 +6181,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6111,8 +6279,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6206,103 +6377,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>421100</v>
+      </c>
+      <c r="E72" s="3">
         <v>418100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>410900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>409700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>399400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>393100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>471400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>461400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>452900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>438100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>414100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>396800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>367800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>342600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>320900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>392900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>380500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>368200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>362000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>359600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>358600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>350400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>341900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>338800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>329300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>321300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>314700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>309400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>307800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>293400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6396,8 +6573,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6491,8 +6671,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6586,103 +6769,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E76" s="3">
         <v>331700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>335300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>333200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>322100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>316700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>398500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>387000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>378000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>363700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>338100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>319100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>288500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>264700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>241300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>311500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>297800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>285500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>277600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>275800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>273900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>264200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>254200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>249400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>238500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>230100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>222500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>227600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>225000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>265900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6776,203 +6965,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E81" s="3">
         <v>10200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>38100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>44400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>38200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>13000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>15200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>10300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>22200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7006,16 +7204,17 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3">
         <v>2800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>6500</v>
       </c>
       <c r="F83" s="3">
         <v>6500</v>
@@ -7024,34 +7223,34 @@
         <v>6500</v>
       </c>
       <c r="H83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I83" s="3">
         <v>5700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>6700</v>
       </c>
       <c r="J83" s="3">
         <v>6700</v>
       </c>
       <c r="K83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="L83" s="3">
         <v>6800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>7300</v>
       </c>
       <c r="N83" s="3">
         <v>7300</v>
       </c>
       <c r="O83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="P83" s="3">
         <v>7500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5900</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>7200</v>
       </c>
       <c r="R83" s="3">
         <v>7200</v>
@@ -7060,10 +7259,10 @@
         <v>7200</v>
       </c>
       <c r="T83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="U83" s="3">
         <v>6900</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7500</v>
       </c>
       <c r="V83" s="3">
         <v>7500</v>
@@ -7075,7 +7274,7 @@
         <v>7500</v>
       </c>
       <c r="Y83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="Z83" s="3">
         <v>8200</v>
@@ -7087,22 +7286,25 @@
         <v>8200</v>
       </c>
       <c r="AC83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AD83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>9300</v>
       </c>
       <c r="AE83" s="3">
         <v>9300</v>
       </c>
       <c r="AF83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AG83" s="3">
         <v>10100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7196,8 +7398,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7291,8 +7496,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7386,8 +7594,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7481,8 +7692,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7576,103 +7790,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>16600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>55300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>48400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>61800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>47000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>40700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>15400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>24200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>14600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>35700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>45300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>42200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>19100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>21000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>18900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>19400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7706,103 +7926,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7896,8 +8120,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7991,103 +8218,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>13000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>35500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-48100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-33900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-61500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>102900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-20200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>12100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-119900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8121,103 +8354,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-6400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-5700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-95800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-7200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-8300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-12000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-15200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-13900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-17600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-15100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-12500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-94800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-6200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-5100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-4900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AF96" s="3">
         <v>-7800</v>
       </c>
       <c r="AG96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8311,8 +8548,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8406,8 +8646,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8501,103 +8744,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-97900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-94800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8691,99 +8940,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-57100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>20500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-20300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-99300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>29000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>39200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,444 +656,457 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E8" s="3">
         <v>136800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>130600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>120900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>142800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>139400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>140700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>166600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>168000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>178200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>184400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>169300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>145700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>130300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>123600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>105100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>95000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>96300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>114000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>121100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>114900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>128400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>131200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>118200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>104800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>131900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>167400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>161800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E9" s="3">
         <v>107400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>98400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>96200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>104700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>111000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>109700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>97100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>108500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>104600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>113400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>121300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>111800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>105100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>94600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>90200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>87600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>80400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>75100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>74000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>81400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>87300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>86900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>91800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>95300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>85100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>74600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>96900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>111600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>108400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E10" s="3">
         <v>29400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>32200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>38500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>39500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>43600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>58100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>63400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>64800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>78800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>72600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>64200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>51100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>40100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>36000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>32600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>33800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>28000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>36600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>35900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>33100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>30200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>35000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>55800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>53400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1128,8 +1141,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,8 +1240,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,8 +1341,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1422,8 +1442,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1520,8 +1543,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1553,204 +1579,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>121800</v>
+      </c>
+      <c r="E17" s="3">
         <v>129300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>120300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>114600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>124400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>132400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>129500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>119500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>115500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>127800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>123300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>131500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>140400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>127200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>112800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>106200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>103500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>95300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>89400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>88900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>97600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>104000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>103000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>109000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>112600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>104400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>91500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>116600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>133500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>130200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>38800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>44700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>59700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>52000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>42100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>24100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>15300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>33900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>31600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1785,204 +1818,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1900</v>
       </c>
       <c r="G20" s="3">
         <v>1900</v>
       </c>
       <c r="H20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>900</v>
       </c>
       <c r="L20" s="3">
         <v>900</v>
       </c>
       <c r="M20" s="3">
+        <v>900</v>
+      </c>
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>700</v>
       </c>
       <c r="T20" s="3">
         <v>700</v>
       </c>
       <c r="U20" s="3">
+        <v>700</v>
+      </c>
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
-      </c>
-      <c r="W20" s="3">
-        <v>1000</v>
       </c>
       <c r="X20" s="3">
         <v>1000</v>
       </c>
       <c r="Y20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>300</v>
       </c>
       <c r="AF20" s="3">
         <v>300</v>
       </c>
       <c r="AG20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH20" s="3">
         <v>700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E21" s="3">
         <v>14900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>27700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>50100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>67500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>59900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>48500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>40200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>15900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>24900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>25000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>20400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>28200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>27100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>20800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>25000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>43500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>42500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1993,35 +2033,35 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -2029,28 +2069,28 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
       <c r="U22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
@@ -2061,8 +2101,8 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2079,204 +2119,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E23" s="3">
         <v>9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>39500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>48000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>60300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>52400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>42600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>32900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>17600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>12200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>14300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>13400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>15700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>34200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>32400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>12000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2373,204 +2422,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E26" s="3">
         <v>7100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>38100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>44400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>38200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>24800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>13000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E27" s="3">
         <v>7100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>38100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>35200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>38200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>24800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>13000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>22200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2667,8 +2725,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2729,8 +2790,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2747,11 +2808,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>500</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2765,8 +2826,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2863,8 +2927,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2961,204 +3028,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1900</v>
       </c>
       <c r="G32" s="3">
         <v>-1900</v>
       </c>
       <c r="H32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-900</v>
       </c>
       <c r="L32" s="3">
         <v>-900</v>
       </c>
       <c r="M32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-700</v>
       </c>
       <c r="T32" s="3">
         <v>-700</v>
       </c>
       <c r="U32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-1000</v>
       </c>
       <c r="X32" s="3">
         <v>-1000</v>
       </c>
       <c r="Y32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-300</v>
       </c>
       <c r="AF32" s="3">
         <v>-300</v>
       </c>
       <c r="AG32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E33" s="3">
         <v>7100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>38100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>35200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>44400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>38200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>24800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>13000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>15200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3255,209 +3331,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E35" s="3">
         <v>7100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>38100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>35200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>44400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>38200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>24800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>13000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>15200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3492,8 +3577,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3528,177 +3614,181 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E41" s="3">
         <v>15800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>38000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>35400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>32200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>35400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>137800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>131700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>102700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>63500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>45400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>44000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>35100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>87100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>98500</v>
+      </c>
+      <c r="E42" s="3">
         <v>99500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>102500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>106500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>126200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>122000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>159100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>165300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>165000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>170000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>200000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>165000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>150000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>122000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>121000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>104000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>208900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>149600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>129500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>114500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>99600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>99500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>114300</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
@@ -3715,8 +3805,8 @@
       <c r="AE42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -3724,400 +3814,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E43" s="3">
         <v>65800</v>
-      </c>
-      <c r="E43" s="3">
-        <v>59900</v>
       </c>
       <c r="F43" s="3">
         <v>59900</v>
       </c>
       <c r="G43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="H43" s="3">
         <v>53100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>65200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>65400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>61400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>69300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>57000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>71900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>76100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>73200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>57900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>58200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>53700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>55800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>52600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>56000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>41500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>52200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>45000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>46800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>50100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>61100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>60100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>53200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>55600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>77600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>69400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E44" s="3">
         <v>68500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>79800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>79300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>69400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>62000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>65000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>61500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>57100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>46900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>43900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>39100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>32000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>28800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>29100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>28300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>33000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>41500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>36500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>31400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>26200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>24000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>26100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>52200</v>
       </c>
       <c r="AE44" s="3">
         <v>52200</v>
       </c>
       <c r="AF44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AG44" s="3">
         <v>55000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>54500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E45" s="3">
         <v>9000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E46" s="3">
         <v>258600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>271400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>274000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>268100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>264000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>361800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>351000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>334100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>336300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>328700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>308900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>285600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>252200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>234400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>213000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>294900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>264600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>249300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>229900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>220500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>226700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>232200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>214400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>208500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>192900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>166800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>153300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>154200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>170900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>214800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4214,106 +4319,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E48" s="3">
         <v>70400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>74300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>72700</v>
       </c>
       <c r="G48" s="3">
         <v>72700</v>
       </c>
       <c r="H48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="I48" s="3">
         <v>75800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>80500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>74000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>77700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>80700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>75300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>66300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>69500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>70800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>72900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>62700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>67900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>73300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>76500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>72100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>74300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>80700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>82700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>84400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>90000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>97100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>103800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>91600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>96600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>102200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>104200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4410,8 +4521,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4508,8 +4622,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4606,106 +4723,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E52" s="3">
         <v>56000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>53700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>56200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>49300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>44900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43800</v>
-      </c>
-      <c r="P52" s="3">
-        <v>41000</v>
       </c>
       <c r="Q52" s="3">
         <v>41000</v>
       </c>
       <c r="R52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="S52" s="3">
         <v>34900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>27000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>24400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>23100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>24300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>13300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>13700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>32600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>33300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>31000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>27900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4802,106 +4925,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E54" s="3">
         <v>385000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>398800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>400400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>396900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>389100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>484800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>460900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>443700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>446500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>442300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>420100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>398900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>364100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>348300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>310600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>389900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>362400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>349000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>328500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>320900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>331700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>335500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>316100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>312800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>303300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>284300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>277500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>284100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>304100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>346900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4936,8 +5065,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4972,106 +5102,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E57" s="3">
         <v>29100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>31000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>38100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>36600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>28800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>29300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>21900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>27800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>33000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>30200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>28900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>28200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>32400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>30800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>34600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>45300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5168,204 +5302,213 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>128100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>32700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>38500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>45100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>36600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>33700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>31900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>38200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>31600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>33500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>35900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>20300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>23500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>21800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>33100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>32400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E60" s="3">
         <v>50100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>59900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>163100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>60200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>54500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>66200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>77100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>80400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>77700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>73000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>81800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>67400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>76300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>62500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>61200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>48700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>55600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>71200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>61800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>62400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>64000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>52700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>54300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>56400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>78400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>80900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5462,106 +5605,112 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E62" s="3">
         <v>3000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3900</v>
       </c>
       <c r="F62" s="3">
         <v>3900</v>
       </c>
       <c r="G62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H62" s="3">
         <v>3800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2200</v>
-      </c>
-      <c r="K62" s="3">
-        <v>2300</v>
       </c>
       <c r="L62" s="3">
         <v>2300</v>
       </c>
       <c r="M62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="N62" s="3">
         <v>1600</v>
       </c>
       <c r="O62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>100</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
       </c>
       <c r="AA62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB62" s="3">
         <v>1000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5658,8 +5807,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5756,8 +5908,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5854,106 +6009,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E66" s="3">
         <v>53000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>67100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>65000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>67000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>168000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>62400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>56800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>68500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>78700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>82000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>79700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>75600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>83600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>69300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>78300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>63500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>45100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>71300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>61900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>63300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>64800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>55000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>56500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>79100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>81000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5988,8 +6149,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6086,8 +6248,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6184,8 +6349,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6282,8 +6450,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6380,106 +6551,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>426600</v>
+      </c>
+      <c r="E72" s="3">
         <v>421100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>418100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>410900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>409700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>399400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>393100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>471400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>461400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>452900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>438100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>414100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>396800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>367800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>342600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>320900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>392900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>380500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>368200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>362000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>359600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>358600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>350400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>341900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>338800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>329300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>321300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>314700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>309400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>307800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>293400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6576,8 +6753,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6674,8 +6854,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6772,106 +6955,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>321500</v>
+      </c>
+      <c r="E76" s="3">
         <v>332000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>331700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>335300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>333200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>322100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>316700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>398500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>387000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>378000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>363700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>338100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>319100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>288500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>264700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>241300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>311500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>297800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>285500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>277600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>275800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>273900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>264200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>254200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>249400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>238500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>230100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>222500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>227600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>225000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>265900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6968,209 +7157,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E81" s="3">
         <v>7100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>38100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>35200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>44400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>38200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>24800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>13000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>15200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7205,19 +7403,20 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E83" s="3">
         <v>5800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>6500</v>
       </c>
       <c r="G83" s="3">
         <v>6500</v>
@@ -7226,34 +7425,34 @@
         <v>6500</v>
       </c>
       <c r="I83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J83" s="3">
         <v>5700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6700</v>
       </c>
       <c r="K83" s="3">
         <v>6700</v>
       </c>
       <c r="L83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="M83" s="3">
         <v>6800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>7300</v>
       </c>
       <c r="O83" s="3">
         <v>7300</v>
       </c>
       <c r="P83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>7500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>7200</v>
       </c>
       <c r="S83" s="3">
         <v>7200</v>
@@ -7262,10 +7461,10 @@
         <v>7200</v>
       </c>
       <c r="U83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="V83" s="3">
         <v>6900</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7500</v>
       </c>
       <c r="W83" s="3">
         <v>7500</v>
@@ -7277,7 +7476,7 @@
         <v>7500</v>
       </c>
       <c r="Z83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="AA83" s="3">
         <v>8200</v>
@@ -7289,22 +7488,25 @@
         <v>8200</v>
       </c>
       <c r="AD83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AE83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>9300</v>
       </c>
       <c r="AF83" s="3">
         <v>9300</v>
       </c>
       <c r="AG83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AH83" s="3">
         <v>10100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7401,8 +7603,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7499,8 +7704,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7597,8 +7805,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7695,8 +7906,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7793,106 +8007,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E89" s="3">
         <v>7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>55300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>48400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>61800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>47000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>40700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>15400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>24200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>45300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>42200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>19100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>21000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>18900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>19400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7927,106 +8147,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8123,8 +8347,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8221,106 +8448,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E94" s="3">
         <v>1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>13000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>35500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-61500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>102900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-61100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-26100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-20200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>12100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-119900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8355,106 +8588,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-4100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-6400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-5700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-95800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-7200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-8300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-15200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-13900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-17600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-15100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-9800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-94800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-6200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-5100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AG96" s="3">
         <v>-7800</v>
       </c>
       <c r="AH96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8551,8 +8788,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8649,8 +8889,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8747,106 +8990,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-97900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-94800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8943,102 +9192,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-57100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-99300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>29000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>8900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,457 +656,470 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E8" s="3">
         <v>130800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>136800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>130600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>120900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>142800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>149200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>139400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>140700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>166600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>168000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>178200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>184400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>169300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>145700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>130300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>123600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>105100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>95000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>96300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>114000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>121100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>114900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>128400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>131200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>118200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>104800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>131900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>167400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>161800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E9" s="3">
         <v>101600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>107400</v>
       </c>
-      <c r="F9" s="3">
-        <v>98400</v>
-      </c>
       <c r="G9" s="3">
+        <v>97900</v>
+      </c>
+      <c r="H9" s="3">
         <v>96200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>104700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>111000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>109700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>97100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>108500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>113400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>121300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>111800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>105100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>94600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>90200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>87600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>80400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>75100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>74000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>81400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>87300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>86900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>91800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>95300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>85100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>74600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>96900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>111600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>108400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E10" s="3">
         <v>29200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29400</v>
       </c>
-      <c r="F10" s="3">
-        <v>32200</v>
-      </c>
       <c r="G10" s="3">
+        <v>32800</v>
+      </c>
+      <c r="H10" s="3">
         <v>24700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>38100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>39500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>43600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>58100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>63400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>64800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>78800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>72600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>64200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>51100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>40100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>36000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>24700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>32600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>33800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>28000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>36600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>35900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>33100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>30200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>35000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>55800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>53400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1155,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1156,8 +1170,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>9800</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1243,8 +1257,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,31 +1361,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1445,31 +1465,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1546,8 +1569,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,210 +1606,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>118500</v>
+      </c>
+      <c r="E17" s="3">
         <v>121800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>129300</v>
       </c>
-      <c r="F17" s="3">
-        <v>120300</v>
-      </c>
       <c r="G17" s="3">
+        <v>119800</v>
+      </c>
+      <c r="H17" s="3">
         <v>114600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>124400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>132400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>129500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>119500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>115500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>127800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>123300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>131500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>140400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>132400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>127200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>112800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>106200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>103500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>95300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>89400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>88900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>97600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>104000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>103000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>109000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>112600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>104400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>91500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>116600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>133500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>130200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7500</v>
       </c>
-      <c r="F18" s="3">
-        <v>10300</v>
-      </c>
       <c r="G18" s="3">
+        <v>10800</v>
+      </c>
+      <c r="H18" s="3">
         <v>6300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>19700</v>
+      </c>
+      <c r="L18" s="3">
+        <v>19900</v>
+      </c>
+      <c r="M18" s="3">
+        <v>25200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>38800</v>
+      </c>
+      <c r="O18" s="3">
+        <v>44700</v>
+      </c>
+      <c r="P18" s="3">
+        <v>46700</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>59700</v>
+      </c>
+      <c r="R18" s="3">
+        <v>52000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>42100</v>
+      </c>
+      <c r="T18" s="3">
+        <v>32900</v>
+      </c>
+      <c r="U18" s="3">
+        <v>24100</v>
+      </c>
+      <c r="V18" s="3">
+        <v>20100</v>
+      </c>
+      <c r="W18" s="3">
+        <v>9800</v>
+      </c>
+      <c r="X18" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AA18" s="3">
         <v>17100</v>
       </c>
-      <c r="J18" s="3">
-        <v>19700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>19900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>25200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>38800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>44700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>46700</v>
-      </c>
-      <c r="P18" s="3">
-        <v>59700</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>52000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>42100</v>
-      </c>
-      <c r="S18" s="3">
-        <v>32900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>24100</v>
-      </c>
-      <c r="U18" s="3">
-        <v>20100</v>
-      </c>
-      <c r="V18" s="3">
-        <v>9800</v>
-      </c>
-      <c r="W18" s="3">
-        <v>5600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>7400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>16400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>17100</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>18600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>13300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>33900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>31600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1819,210 +1852,217 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1500</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
-        <v>1600</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>1700</v>
+        <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>1900</v>
+        <v>-400</v>
       </c>
       <c r="H20" s="3">
-        <v>1900</v>
+        <v>-400</v>
       </c>
       <c r="I20" s="3">
-        <v>1400</v>
+        <v>-400</v>
       </c>
       <c r="J20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>900</v>
       </c>
       <c r="M20" s="3">
         <v>900</v>
       </c>
       <c r="N20" s="3">
+        <v>900</v>
+      </c>
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>700</v>
       </c>
       <c r="U20" s="3">
         <v>700</v>
       </c>
       <c r="V20" s="3">
+        <v>700</v>
+      </c>
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>900</v>
-      </c>
-      <c r="X20" s="3">
-        <v>1000</v>
       </c>
       <c r="Y20" s="3">
         <v>1000</v>
       </c>
       <c r="Z20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>300</v>
       </c>
       <c r="AG20" s="3">
         <v>300</v>
       </c>
       <c r="AH20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI20" s="3">
         <v>700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>15800</v>
+        <v>9900</v>
       </c>
       <c r="E21" s="3">
-        <v>14900</v>
+        <v>14500</v>
       </c>
       <c r="F21" s="3">
-        <v>14800</v>
+        <v>13500</v>
       </c>
       <c r="G21" s="3">
-        <v>14700</v>
+        <v>14000</v>
       </c>
       <c r="H21" s="3">
-        <v>26800</v>
+        <v>13300</v>
       </c>
       <c r="I21" s="3">
-        <v>25100</v>
+        <v>25300</v>
       </c>
       <c r="J21" s="3">
+        <v>23800</v>
+      </c>
+      <c r="K21" s="3">
         <v>27400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>46400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>50100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>67500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>59900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>48500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>31900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>15900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>24900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>25000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>20400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>27100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>20800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>25000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>43500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>42500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2036,35 +2076,35 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2072,28 +2112,28 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
       <c r="V22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
@@ -2104,8 +2144,8 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2122,210 +2162,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>10500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>39500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>48000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>60300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>52400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>42600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>32900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>17400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>17600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>12200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>18900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>14300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>13400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>34200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>32400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>12000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>11500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2425,210 +2474,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E26" s="3">
         <v>8300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>38100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>35200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>44400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>38200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>13000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>22200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E27" s="3">
         <v>8300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>20800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>38100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>44400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>38200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>13000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>12300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>14300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>22200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2728,8 +2786,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2793,8 +2854,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2811,11 +2872,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>500</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2829,8 +2890,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2930,8 +2994,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3031,210 +3098,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1500</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
-        <v>-1600</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>-1700</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>-1900</v>
+        <v>400</v>
       </c>
       <c r="H32" s="3">
-        <v>-1900</v>
+        <v>400</v>
       </c>
       <c r="I32" s="3">
-        <v>-1400</v>
+        <v>400</v>
       </c>
       <c r="J32" s="3">
+        <v>300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-900</v>
       </c>
       <c r="M32" s="3">
         <v>-900</v>
       </c>
       <c r="N32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-700</v>
       </c>
       <c r="U32" s="3">
         <v>-700</v>
       </c>
       <c r="V32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-900</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y32" s="3">
         <v>-1000</v>
       </c>
       <c r="Z32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-300</v>
       </c>
       <c r="AG32" s="3">
         <v>-300</v>
       </c>
       <c r="AH32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E33" s="3">
         <v>8300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>20800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>38100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>44400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>38200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>13000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>12300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>15200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>10200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>22200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3334,215 +3410,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E35" s="3">
         <v>8300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>20800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>38100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>44400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>38200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>13000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>12300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>15200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>10200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>22200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3578,8 +3663,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3615,183 +3701,187 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E41" s="3">
         <v>7200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>29700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>38000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>35400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>32200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>35400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>38500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>137800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>131700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>102700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>63500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>45400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>44000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>35100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>87100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E42" s="3">
         <v>98500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>99500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>102500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>106500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>126200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>122000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>159100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>165300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>165000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>170000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>200000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>165000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>150000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>122000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>121000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>104000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>208900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>149600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>129500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>114500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>99600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>99500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>114300</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>8</v>
@@ -3808,8 +3898,8 @@
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH42" s="3">
         <v>0</v>
@@ -3817,435 +3907,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E43" s="3">
         <v>56100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>65800</v>
-      </c>
-      <c r="F43" s="3">
-        <v>59900</v>
       </c>
       <c r="G43" s="3">
         <v>59900</v>
       </c>
       <c r="H43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="I43" s="3">
         <v>53100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>65200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>65400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>61400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>56200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>69300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>57000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>71900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>76100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>73200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>57900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>53700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>55800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>52600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>56000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>41500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>52200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>45000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>46800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>50100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>61100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>60100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>53200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>55600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>77600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>69400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E44" s="3">
         <v>73300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>68500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>79800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>79300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>69400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>62000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>65000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>61500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>57100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>46900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>43900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>39100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>32000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>28800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>29100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>18300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>28300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>33000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>41500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>36500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>31400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>26200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>24000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>26100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>52200</v>
       </c>
       <c r="AF44" s="3">
         <v>52200</v>
       </c>
       <c r="AG44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AH44" s="3">
         <v>55000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>54500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>16900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>14100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>14800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>6700</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>7100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>247100</v>
+      </c>
+      <c r="E46" s="3">
         <v>252000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>258600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>271400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>274000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>268100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>264000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>361800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>351000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>334100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>336300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>328700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>308900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>285600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>252200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>234400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>213000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>294900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>264600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>249300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>229900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>220500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>226700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>232200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>214400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>208500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>192900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>166800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>153300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>154200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>170900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>214800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4322,109 +4427,115 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E48" s="3">
         <v>73800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>70400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>74300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>72700</v>
       </c>
       <c r="H48" s="3">
         <v>72700</v>
       </c>
       <c r="I48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="J48" s="3">
         <v>75800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>80500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>74000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>77700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>80700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>75300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>66300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>69500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>70800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>72900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>62700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>67900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>73300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>76500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>72100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>74300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>80700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>82700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>84400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>90000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>97100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>103800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>91600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>96600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>102200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>104200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4438,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -4524,8 +4635,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4625,8 +4739,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4726,109 +4843,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>51000</v>
+        <v>36600</v>
       </c>
       <c r="E52" s="3">
-        <v>56000</v>
+        <v>36200</v>
       </c>
       <c r="F52" s="3">
-        <v>53100</v>
+        <v>40900</v>
       </c>
       <c r="G52" s="3">
-        <v>53700</v>
+        <v>30200</v>
       </c>
       <c r="H52" s="3">
-        <v>56200</v>
+        <v>43500</v>
       </c>
       <c r="I52" s="3">
-        <v>49300</v>
+        <v>46100</v>
       </c>
       <c r="J52" s="3">
+        <v>43100</v>
+      </c>
+      <c r="K52" s="3">
         <v>42400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>44900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43800</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>41000</v>
       </c>
       <c r="R52" s="3">
         <v>41000</v>
       </c>
       <c r="S52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="T52" s="3">
         <v>34900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>27000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>24400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>23100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>24300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>17200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>13300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>13700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>32600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>33300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>31000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>27900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4928,109 +5051,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>373500</v>
+      </c>
+      <c r="E54" s="3">
         <v>376700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>385000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>398800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>400400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>396900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>389100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>484800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>460900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>443700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>446500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>442300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>420100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>398900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>364100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>348300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>310600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>389900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>362400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>349000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>328500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>320900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>331700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>335500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>316100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>312800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>303300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>284300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>277500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>284100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>304100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>346900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5066,8 +5195,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5103,132 +5233,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E57" s="3">
         <v>29000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29100</v>
       </c>
-      <c r="F57" s="3">
-        <v>31100</v>
-      </c>
       <c r="G57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="H57" s="3">
         <v>29100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>37900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>39700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>28800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>29300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>24600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>27800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>33000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>30200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>28900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>28200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>32400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>30800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>34600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>45300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>48500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5305,233 +5439,242 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>23000</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>128100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>29200</v>
+      </c>
+      <c r="M59" s="3">
+        <v>27500</v>
+      </c>
+      <c r="N59" s="3">
+        <v>32700</v>
+      </c>
+      <c r="O59" s="3">
+        <v>41000</v>
+      </c>
+      <c r="P59" s="3">
+        <v>42300</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>39800</v>
+      </c>
+      <c r="R59" s="3">
+        <v>38500</v>
+      </c>
+      <c r="S59" s="3">
+        <v>45100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>40300</v>
+      </c>
+      <c r="U59" s="3">
+        <v>36600</v>
+      </c>
+      <c r="V59" s="3">
+        <v>33700</v>
+      </c>
+      <c r="W59" s="3">
+        <v>31900</v>
+      </c>
+      <c r="X59" s="3">
+        <v>24100</v>
+      </c>
+      <c r="Y59" s="3">
         <v>21000</v>
       </c>
-      <c r="F59" s="3">
-        <v>32100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>32000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>30200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>28900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>128100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>29200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>27500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>32700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>41000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>42300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>39800</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>38500</v>
-      </c>
-      <c r="R59" s="3">
-        <v>45100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>40300</v>
-      </c>
-      <c r="T59" s="3">
-        <v>36600</v>
-      </c>
-      <c r="U59" s="3">
-        <v>33700</v>
-      </c>
-      <c r="V59" s="3">
-        <v>31900</v>
-      </c>
-      <c r="W59" s="3">
-        <v>24100</v>
-      </c>
-      <c r="X59" s="3">
-        <v>21000</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>27700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>38200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>31600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>35900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>20300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>23500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>21800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>33100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>32400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E60" s="3">
         <v>52000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>50100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>63200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>163100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>60200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>54500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>66200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>77100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>80400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>77700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>73000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>81800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>67400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>76300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>62500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>61200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>48700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>43000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>55600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>71200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>61800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>62400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>64000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>52700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>54300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>56400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>78400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>80900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5608,109 +5751,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>3900</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>5000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2300</v>
       </c>
       <c r="M62" s="3">
         <v>2300</v>
       </c>
       <c r="N62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="O62" s="3">
         <v>1600</v>
       </c>
       <c r="P62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2200</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>100</v>
       </c>
       <c r="AA62" s="3">
         <v>100</v>
       </c>
       <c r="AB62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC62" s="3">
         <v>1000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5810,8 +5959,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5911,8 +6063,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6012,109 +6167,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E66" s="3">
         <v>55200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>67100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>65000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>67000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>168000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>56800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>68500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>78700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>82000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>79700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>75600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>83600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>69300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>78300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>63500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>50900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>45100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>71300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>61900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>63300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>64800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>54200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>55000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>56500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>79100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>81000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6150,8 +6311,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6251,8 +6413,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6352,8 +6517,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6453,8 +6621,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6554,109 +6725,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E72" s="3">
         <v>426600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>421100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>418100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>410900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>409700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>399400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>393100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>471400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>461400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>452900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>438100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>414100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>396800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>367800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>342600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>320900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>392900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>380500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>368200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>362000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>359600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>358600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>350400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>341900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>338800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>329300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>321300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>314700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>309400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>307800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>293400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6756,8 +6933,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6857,8 +7037,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6958,109 +7141,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>314900</v>
+      </c>
+      <c r="E76" s="3">
         <v>321500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>332000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>331700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>335300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>333200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>322100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>316700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>398500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>387000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>378000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>363700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>338100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>319100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>288500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>264700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>241300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>311500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>297800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>285500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>277600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>275800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>273900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>264200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>254200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>249400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>238500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>230100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>222500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>227600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>225000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>265900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7160,215 +7349,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E81" s="3">
         <v>8300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>20800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>38100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>44400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>38200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>13000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>12300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>15200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>10200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>22200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7404,58 +7602,59 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G83" s="3">
         <v>5300</v>
       </c>
-      <c r="E83" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>6500</v>
-      </c>
       <c r="H83" s="3">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="I83" s="3">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="J83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K83" s="3">
         <v>5700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6700</v>
       </c>
       <c r="L83" s="3">
         <v>6700</v>
       </c>
       <c r="M83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N83" s="3">
         <v>6800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>7300</v>
       </c>
       <c r="P83" s="3">
         <v>7300</v>
       </c>
       <c r="Q83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R83" s="3">
         <v>7500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5900</v>
-      </c>
-      <c r="S83" s="3">
-        <v>7200</v>
       </c>
       <c r="T83" s="3">
         <v>7200</v>
@@ -7464,10 +7663,10 @@
         <v>7200</v>
       </c>
       <c r="V83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="W83" s="3">
         <v>6900</v>
-      </c>
-      <c r="W83" s="3">
-        <v>7500</v>
       </c>
       <c r="X83" s="3">
         <v>7500</v>
@@ -7479,7 +7678,7 @@
         <v>7500</v>
       </c>
       <c r="AA83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="AB83" s="3">
         <v>8200</v>
@@ -7491,22 +7690,25 @@
         <v>8200</v>
       </c>
       <c r="AE83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AF83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>9300</v>
       </c>
       <c r="AG83" s="3">
         <v>9300</v>
       </c>
       <c r="AH83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AI83" s="3">
         <v>10100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7606,8 +7808,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7707,8 +7912,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7808,8 +8016,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7909,8 +8120,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8010,109 +8224,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E89" s="3">
         <v>18700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>27000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>55300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>48400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>61800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>47000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>31100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>40700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>24200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>14600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>45300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>42200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>19100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>21000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>18900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>19400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8148,109 +8368,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8350,8 +8574,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8451,109 +8678,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>35500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-48100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>102900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-61100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-24200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-26100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>12100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-119900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8589,109 +8822,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2700</v>
+        <v>3200</v>
       </c>
       <c r="E96" s="3">
-        <v>-4100</v>
+        <v>2700</v>
       </c>
       <c r="F96" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H96" s="3">
+        <v>94700</v>
+      </c>
+      <c r="I96" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J96" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="M96" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="N96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="O96" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="P96" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="R96" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="S96" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="T96" s="3">
+        <v>-94800</v>
+      </c>
+      <c r="U96" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3000</v>
       </c>
-      <c r="G96" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-95800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-17600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-94800</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AH96" s="3">
         <v>-7800</v>
       </c>
       <c r="AI96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8791,8 +9028,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8892,8 +9132,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8993,132 +9236,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-97900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-17300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-94800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9195,105 +9444,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-57100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-99300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>29000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>39200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>18100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,470 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E8" s="3">
         <v>122300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>130800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>136800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>130600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>120900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>142800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>149500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>149200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>139400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>140700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>166600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>168000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>178200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>200100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>184400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>169300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>145700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>130300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>123600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>105100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>95000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>96300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>114000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>121100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>114900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>128400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>131200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>118200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>104800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>131900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>167400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>161800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>112500</v>
+      </c>
+      <c r="E9" s="3">
         <v>99600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>101600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>107400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>97900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>96200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>104700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>111000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>109700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>100500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>97100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>108500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>113400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>121300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>111800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>105100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>94600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>90200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>87600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>80400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>75100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>74000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>81400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>87300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>86900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>91800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>95300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>85100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>74600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>96900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>111600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>108400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E10" s="3">
         <v>22700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>43600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>58100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>63400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>64800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>78800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>72600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>64200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>51100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>40100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>36000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>24700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>22300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>32600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>33800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>28000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>36600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>35900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>33100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>30200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>35000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>55800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>53400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1156,13 +1168,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>8200</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1170,11 +1183,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>9800</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1260,8 +1273,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1364,13 +1380,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>1600</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1378,11 +1397,11 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1390,8 +1409,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1468,25 +1487,28 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E15" s="3">
         <v>5800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>6500</v>
       </c>
       <c r="I15" s="3">
         <v>6500</v>
@@ -1495,7 +1517,7 @@
         <v>6500</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1572,8 +1594,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1607,216 +1632,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>132800</v>
+      </c>
+      <c r="E17" s="3">
         <v>118500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>121800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>129300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>119800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>114600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>124400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>132400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>129500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>119500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>115500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>127800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>123300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>131500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>140400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>132400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>127200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>112800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>106200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>103500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>95300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>89400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>88900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>97600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>104000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>103000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>109000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>112600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>104400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>91500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>116600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>133500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>130200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>44700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>59700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>52000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>42100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>19400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>18600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>13800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>13300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>33900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>31600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1853,22 +1885,23 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-200</v>
       </c>
       <c r="F20" s="3">
         <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
         <v>-400</v>
@@ -1877,192 +1910,198 @@
         <v>-400</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>900</v>
       </c>
       <c r="N20" s="3">
         <v>900</v>
       </c>
       <c r="O20" s="3">
+        <v>900</v>
+      </c>
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>700</v>
       </c>
       <c r="V20" s="3">
         <v>700</v>
       </c>
       <c r="W20" s="3">
+        <v>700</v>
+      </c>
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>900</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1000</v>
       </c>
       <c r="Z20" s="3">
         <v>1000</v>
       </c>
       <c r="AA20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>300</v>
       </c>
       <c r="AH20" s="3">
         <v>300</v>
       </c>
       <c r="AI20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E21" s="3">
         <v>9900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>25300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>46400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>50100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>55400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>67500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>59900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>48500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>40200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>31900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>25000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>20400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>28200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>27100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>22600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>20800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>25000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>43500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>42500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2079,35 +2118,35 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2115,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
       <c r="W22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3">
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
@@ -2147,8 +2186,8 @@
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2165,216 +2204,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>39500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>48000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>60300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>52400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>42600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>32900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>20800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>17400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>17600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>12200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>18900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>14300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>13400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>15700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>34200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>12000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2477,216 +2525,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E26" s="3">
         <v>4700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>38100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>44400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>38200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>13000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>9400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>10200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>22200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E27" s="3">
         <v>4700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>38100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>44400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>38200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>13000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>15200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>14300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>22200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2789,8 +2846,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2857,8 +2917,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2875,11 +2935,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>500</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2893,8 +2953,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2997,8 +3060,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3101,22 +3167,25 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>200</v>
       </c>
       <c r="F32" s="3">
         <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
         <v>400</v>
@@ -3125,192 +3194,198 @@
         <v>400</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-900</v>
       </c>
       <c r="N32" s="3">
         <v>-900</v>
       </c>
       <c r="O32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-700</v>
       </c>
       <c r="V32" s="3">
         <v>-700</v>
       </c>
       <c r="W32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z32" s="3">
         <v>-1000</v>
       </c>
       <c r="AA32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-300</v>
       </c>
       <c r="AH32" s="3">
         <v>-300</v>
       </c>
       <c r="AI32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E33" s="3">
         <v>4700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>30200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>38100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>44400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>38200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>13000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>15200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>14300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>22200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3413,221 +3488,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E35" s="3">
         <v>4700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>30200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>38100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>44400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>38200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>13000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>15200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>14300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>22200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3664,8 +3748,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3702,189 +3787,193 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>43500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>17700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>38000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>35400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>22800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>32200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>35400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>137800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>131700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>102700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>63500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>45400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>44000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>35100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>87100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E42" s="3">
         <v>88500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>98500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>99500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>102500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>106500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>126200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>122000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>159100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>165300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>165000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>170000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>200000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>165000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>150000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>122000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>121000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>104000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>208900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>149600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>129500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>114500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>99600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>99500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>114300</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>8</v>
@@ -3901,8 +3990,8 @@
       <c r="AG42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH42" s="3">
-        <v>0</v>
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
@@ -3910,216 +3999,225 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E43" s="3">
         <v>60200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>56100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>65800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>59900</v>
       </c>
       <c r="H43" s="3">
         <v>59900</v>
       </c>
       <c r="I43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="J43" s="3">
         <v>53100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>65200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>65400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>61400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>56200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>69300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>57000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>71900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>76100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>73200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>57900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>53700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>55800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>52600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>56000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>41500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>52200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>45000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>46800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>50100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>61100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>60100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>53200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>55600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>77600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>69400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E44" s="3">
         <v>76000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>73300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>68500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>79800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>79300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>69400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>62000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>65000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>61500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>57100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>46900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>43900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>39100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>32000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>28800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>29100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>18300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>28300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>33000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>41500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>36500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>31400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>26200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>24000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>26100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>52200</v>
       </c>
       <c r="AG44" s="3">
         <v>52200</v>
       </c>
       <c r="AH44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AI44" s="3">
         <v>55000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>54500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4144,190 +4242,196 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>7100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>258400</v>
+      </c>
+      <c r="E46" s="3">
         <v>247100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>252000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>258600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>271400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>274000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>268100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>264000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>361800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>351000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>334100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>336300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>328700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>308900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>285600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>252200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>234400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>213000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>294900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>264600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>249300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>229900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>220500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>226700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>232200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>214400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>208500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>192900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>166800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>153300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>154200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>170900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>214800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4352,8 +4456,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4430,117 +4534,123 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E48" s="3">
         <v>74900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>70400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>74300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>72700</v>
       </c>
       <c r="I48" s="3">
         <v>72700</v>
       </c>
       <c r="J48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="K48" s="3">
         <v>75800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>80500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>74000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>77700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>80700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>75300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>66300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>69500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>70800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>72900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>62700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>67900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>73300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>76500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>72100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>74300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>80700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>82700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>84400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>90000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>97100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>103800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>91600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>96600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>102200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>104200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>10100</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4549,11 +4659,11 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>10900</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -4638,8 +4748,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4742,8 +4855,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4846,112 +4962,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E52" s="3">
         <v>36600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>36200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>43500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>46100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>44900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>43800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>41000</v>
       </c>
       <c r="S52" s="3">
         <v>41000</v>
       </c>
       <c r="T52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="U52" s="3">
         <v>34900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>27000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>24400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>23100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>24300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>14300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>13300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>32600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>33300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>31000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5054,112 +5176,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E54" s="3">
         <v>373500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>376700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>385000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>398800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>400400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>396900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>389100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>484800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>460900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>443700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>446500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>442300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>420100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>398900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>364100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>348300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>310600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>389900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>362400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>349000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>328500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>320900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>331700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>335500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>316100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>312800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>303300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>284300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>277500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>284100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>304100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>346900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5196,8 +5324,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5234,112 +5363,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E57" s="3">
         <v>30900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>38100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>37900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>34500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>27100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>39700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>28800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>29300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>24600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>27800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>33000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>30200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>28900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>28200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>32400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>30800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>34600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>45300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>48500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5359,13 +5492,13 @@
         <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>700</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5442,13 +5575,16 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
         <v>300</v>
@@ -5457,228 +5593,234 @@
         <v>300</v>
       </c>
       <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>128100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>29200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>38500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>45100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>40300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>36600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>33700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>31900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>24100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>27700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>38200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>31600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>33500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>35900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>20300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>23500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>21800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>33100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E60" s="3">
         <v>55000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>52000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>63200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>59900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>163100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>60200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>54500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>66200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>77100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>80400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>77700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>73000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>81800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>67400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>76300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>62500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>61200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>48700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>43000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>55600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>71200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>61800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>62400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>64000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>52700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>54300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>56400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>78400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>80900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5754,8 +5896,11 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5769,7 +5914,7 @@
         <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -5781,85 +5926,88 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>5000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2200</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2300</v>
       </c>
       <c r="N62" s="3">
         <v>2300</v>
       </c>
       <c r="O62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="P62" s="3">
         <v>1600</v>
       </c>
       <c r="Q62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R62" s="3">
         <v>2000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2200</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>100</v>
       </c>
       <c r="AB62" s="3">
         <v>100</v>
       </c>
       <c r="AC62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD62" s="3">
         <v>1000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5962,8 +6110,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6066,8 +6217,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6170,112 +6324,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>64500</v>
+      </c>
+      <c r="E66" s="3">
         <v>58500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>67100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>67000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>168000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>56800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>68500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>78700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>82000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>79700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>75600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>83600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>69300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>78300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>64600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>63500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>50900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>45100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>57800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>71300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>61900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>63300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>64800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>54200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>55000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>56500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>79100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6312,8 +6472,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6416,8 +6577,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6520,8 +6684,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6624,8 +6791,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6728,112 +6898,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>436600</v>
+      </c>
+      <c r="E72" s="3">
         <v>428000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>426600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>421100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>418100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>410900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>409700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>399400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>393100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>471400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>461400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>452900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>438100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>414100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>396800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>367800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>342600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>320900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>392900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>380500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>368200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>362000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>359600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>358600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>350400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>341900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>338800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>329300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>321300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>314700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>309400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>307800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>293400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6936,8 +7112,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7040,8 +7219,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7144,112 +7326,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>319600</v>
+      </c>
+      <c r="E76" s="3">
         <v>314900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>321500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>332000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>331700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>335300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>333200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>322100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>316700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>398500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>387000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>378000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>363700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>338100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>319100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>288500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>264700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>241300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>311500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>297800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>285500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>277600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>275800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>273900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>264200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>254200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>249400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>238500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>230100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>222500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>227600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>225000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>265900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7352,221 +7540,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E81" s="3">
         <v>4700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>30200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>38100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>44400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>38200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>13000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>15200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>14300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>22200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7603,13 +7800,14 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6500</v>
+        <v>2400</v>
       </c>
       <c r="E83" s="3">
         <v>6500</v>
@@ -7618,46 +7816,46 @@
         <v>6500</v>
       </c>
       <c r="G83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H83" s="3">
         <v>5300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>6700</v>
       </c>
       <c r="I83" s="3">
         <v>6700</v>
       </c>
       <c r="J83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K83" s="3">
         <v>6800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6700</v>
       </c>
       <c r="M83" s="3">
         <v>6700</v>
       </c>
       <c r="N83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="O83" s="3">
         <v>6800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>7300</v>
       </c>
       <c r="Q83" s="3">
         <v>7300</v>
       </c>
       <c r="R83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="S83" s="3">
         <v>7500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7200</v>
       </c>
       <c r="U83" s="3">
         <v>7200</v>
@@ -7666,10 +7864,10 @@
         <v>7200</v>
       </c>
       <c r="W83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="X83" s="3">
         <v>6900</v>
-      </c>
-      <c r="X83" s="3">
-        <v>7500</v>
       </c>
       <c r="Y83" s="3">
         <v>7500</v>
@@ -7681,7 +7879,7 @@
         <v>7500</v>
       </c>
       <c r="AB83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="AC83" s="3">
         <v>8200</v>
@@ -7693,22 +7891,25 @@
         <v>8200</v>
       </c>
       <c r="AF83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AG83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>9300</v>
       </c>
       <c r="AH83" s="3">
         <v>9300</v>
       </c>
       <c r="AI83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7811,8 +8012,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7915,8 +8119,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8019,8 +8226,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8123,8 +8333,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8227,112 +8440,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>27000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>18800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>55300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>48400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>61800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>47000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>31100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>40700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>15400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>24200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>14600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>45300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>42200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>19100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>21000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>18900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>19400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8369,112 +8588,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8577,8 +8800,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8681,112 +8907,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E94" s="3">
         <v>3300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>13000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>35500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-48100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-33900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-61500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>102900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-61100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-24200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-26100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-20200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>12100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-119900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8823,112 +9055,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E96" s="3">
         <v>3200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4100</v>
       </c>
-      <c r="G96" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>94700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>7500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-7200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-8300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-12000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-15200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-13900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-15100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-12500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-9800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-94800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-6200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-3000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AI96" s="3">
         <v>-7800</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9031,8 +9267,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9135,8 +9374,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9239,112 +9481,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-97900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-94800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9369,8 +9617,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9447,108 +9695,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-57100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-20300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-99300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>29000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>39200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>18100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>8900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,482 +656,495 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>135700</v>
+      </c>
+      <c r="E8" s="3">
         <v>145800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>122300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>130800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>136800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>130600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>120900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>142800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>149500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>149200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>139400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>140700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>166600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>168000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>178200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>200100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>184400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>169300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>145700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>130300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>123600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>105100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>95000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>96300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>114000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>121100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>114900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>128400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>131200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>118200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>104800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>131900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>167400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>161800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>105800</v>
+      </c>
+      <c r="E9" s="3">
         <v>112500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>99600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>101600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>107400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>97900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>96200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>104700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>111000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>109700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>97100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>108500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>104600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>113400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>121300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>111800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>105100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>94600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>90200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>87600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>80400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>75100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>74000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>81400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>87300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>86900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>91800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>95300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>85100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>74600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>96900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>111600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>108400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E10" s="3">
         <v>33300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>29400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>39500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>43600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>58100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>63400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>64800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>78800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>72600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>64200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>51100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>40100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>36000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>24700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>32600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>33800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>28000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>36600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>35900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>33100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>30200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>35000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>55800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>53400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,16 +1182,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>8200</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1186,11 +1200,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>9800</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1276,8 +1290,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1383,16 +1400,19 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>1600</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1400,11 +1420,11 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1412,8 +1432,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1490,28 +1510,31 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E15" s="3">
         <v>5100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>6500</v>
       </c>
       <c r="J15" s="3">
         <v>6500</v>
@@ -1520,7 +1543,7 @@
         <v>6500</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1597,8 +1620,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1633,222 +1659,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E17" s="3">
         <v>132800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>118500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>121800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>129300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>119800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>114600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>124400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>132400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>119500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>115500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>127800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>123300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>131500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>140400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>132400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>127200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>112800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>106200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>103500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>95300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>89400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>88900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>97600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>104000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>103000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>109000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>112600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>104400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>91500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>116600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>133500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>130200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E18" s="3">
         <v>13000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>44700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>59700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>52000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>42100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>17100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>19400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>18600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>13800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>13300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>15300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>33900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>31600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1886,25 +1919,26 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-200</v>
       </c>
       <c r="G20" s="3">
         <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
         <v>-400</v>
@@ -1913,195 +1947,201 @@
         <v>-400</v>
       </c>
       <c r="K20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>900</v>
       </c>
       <c r="O20" s="3">
         <v>900</v>
       </c>
       <c r="P20" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>700</v>
       </c>
       <c r="W20" s="3">
         <v>700</v>
       </c>
       <c r="X20" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>900</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1000</v>
       </c>
       <c r="AA20" s="3">
         <v>1000</v>
       </c>
       <c r="AB20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>300</v>
       </c>
       <c r="AI20" s="3">
         <v>300</v>
       </c>
       <c r="AJ20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK20" s="3">
         <v>700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E21" s="3">
         <v>18700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>25300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>46400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>50100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>55400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>67500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>59900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>48500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>40200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>31900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>13900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>15900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>24900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>25000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>20400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>28200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>27100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>22600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>20800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>25000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>43500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>42500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2121,35 +2161,35 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -2157,28 +2197,28 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
       <c r="X22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
@@ -2189,8 +2229,8 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
@@ -2207,222 +2247,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E23" s="3">
         <v>13000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>39500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>45900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>48000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>60300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>52400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>42600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>32900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>17400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>18900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>14300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>13400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>34200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>32400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>11500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2528,222 +2577,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E26" s="3">
         <v>10500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>38100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>35200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>44400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>38200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>24800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>13000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>9800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>9400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>10200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>20800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E27" s="3">
         <v>10500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>38100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>38200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>13000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>15200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>14300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>10200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>20800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2849,8 +2907,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2920,8 +2981,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2938,11 +2999,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>500</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2956,8 +3017,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3063,8 +3127,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3170,25 +3237,28 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>200</v>
       </c>
       <c r="G32" s="3">
         <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
         <v>400</v>
@@ -3197,195 +3267,201 @@
         <v>400</v>
       </c>
       <c r="K32" s="3">
+        <v>400</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-900</v>
       </c>
       <c r="O32" s="3">
         <v>-900</v>
       </c>
       <c r="P32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-700</v>
       </c>
       <c r="W32" s="3">
         <v>-700</v>
       </c>
       <c r="X32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-900</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA32" s="3">
         <v>-1000</v>
       </c>
       <c r="AB32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-300</v>
       </c>
       <c r="AI32" s="3">
         <v>-300</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E33" s="3">
         <v>10500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>20800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>38100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>44400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>38200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>31700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>15300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>13000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>15200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>14300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>10300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>10200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>20800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3491,227 +3567,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E35" s="3">
         <v>10500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>20800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>38100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>44400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>38200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>31700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>15300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>13000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>15200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>14300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>10300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>10200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>20800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3749,8 +3834,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3788,195 +3874,199 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E41" s="3">
         <v>10000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>21000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>27700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>35400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>22800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>32200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>35400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>137800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>131700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>102700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>63500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>45400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>44000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>35100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>87100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E42" s="3">
         <v>95500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>88500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>98500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>99500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>102500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>106500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>126200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>122000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>159100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>165300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>165000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>170000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>200000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>165000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>150000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>122000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>121000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>104000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>208900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>149600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>129500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>114500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>99600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>99500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>114300</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>8</v>
@@ -3993,8 +4083,8 @@
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ42" s="3">
         <v>0</v>
@@ -4002,222 +4092,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E43" s="3">
         <v>67100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>60200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>56100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>65800</v>
-      </c>
-      <c r="H43" s="3">
-        <v>59900</v>
       </c>
       <c r="I43" s="3">
         <v>59900</v>
       </c>
       <c r="J43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="K43" s="3">
         <v>53100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>65200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>65400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>56200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>69300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>57000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>71900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>76100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>73200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>57900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>58200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>53700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>55800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>52600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>56000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>41500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>52200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>45000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>46800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>50100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>61100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>60100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>53200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>55600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>77600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>69400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E44" s="3">
         <v>76500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>76000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>73300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>68500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>79800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>69400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>62000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>65000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>57100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>46900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>43900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>39100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>32000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>28800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>29100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>28300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>33000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>41500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>36500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>31400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>26200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>24000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>26100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AG44" s="3">
-        <v>52200</v>
       </c>
       <c r="AH44" s="3">
         <v>52200</v>
       </c>
       <c r="AI44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>54500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4245,193 +4344,199 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>7100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>12500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>253400</v>
+      </c>
+      <c r="E46" s="3">
         <v>258400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>247100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>252000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>258600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>271400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>274000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>268100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>264000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>361800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>351000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>334100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>336300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>328700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>308900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>285600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>252200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>234400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>213000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>294900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>264600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>249300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>229900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>220500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>226700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>232200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>214400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>208500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>192900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>166800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>153300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>154200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>170900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>214800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4459,8 +4564,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4537,124 +4642,130 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E48" s="3">
         <v>73600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>74900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>70400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>72700</v>
       </c>
       <c r="J48" s="3">
         <v>72700</v>
       </c>
       <c r="K48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="L48" s="3">
         <v>75800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>80500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>74000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>77700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>80700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>75300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>66300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>69500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>70800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>72900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>62700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>67900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>73300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>76500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>72100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>74300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>80700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>82700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>84400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>90000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>97100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>103800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>91600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>96600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>102200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>104200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>10100</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -4662,11 +4773,11 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>10900</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -4751,8 +4862,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4858,8 +4972,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4965,115 +5082,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E52" s="3">
         <v>25300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>36600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>36200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>43500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>46100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>38300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>44900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43800</v>
-      </c>
-      <c r="S52" s="3">
-        <v>41000</v>
       </c>
       <c r="T52" s="3">
         <v>41000</v>
       </c>
       <c r="U52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="V52" s="3">
         <v>34900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>27000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>23100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>26100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>24300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>14300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>13700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>32600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>33300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>31000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>27900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5179,115 +5302,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>379000</v>
+      </c>
+      <c r="E54" s="3">
         <v>384000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>373500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>376700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>385000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>398800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>400400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>396900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>389100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>484800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>460900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>443700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>446500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>442300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>420100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>398900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>364100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>348300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>310600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>389900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>362400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>349000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>328500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>320900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>331700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>335500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>316100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>312800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>303300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>284300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>277500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>284100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>304100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>346900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5325,8 +5454,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5364,115 +5494,119 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E57" s="3">
         <v>13200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>38100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>37900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>34500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>27100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>28800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>29300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>24600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>27800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>33000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>30200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>28900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>28200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>32400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>30800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>34600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>45300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>48500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5495,13 +5629,13 @@
         <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>700</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5578,16 +5712,19 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>300</v>
@@ -5596,234 +5733,240 @@
         <v>300</v>
       </c>
       <c r="H59" s="3">
+        <v>300</v>
+      </c>
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>39800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>38500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>45100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>40300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>36600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>33700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>31900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>24100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>27700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>38200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>31600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>33500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>35900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>20300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>23500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>21800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>33100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>32400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E60" s="3">
         <v>60800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>52000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>63200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>59900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>61600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>163100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>60200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>54500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>77100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>80400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>77700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>73000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>81800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>67400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>76300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>62500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>61200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>48700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>43000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>55600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>71200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>61800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>62400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>64000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>52700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>54300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>56400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>78400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>80900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5899,8 +6042,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5917,7 +6063,7 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -5929,85 +6075,88 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>5000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2200</v>
-      </c>
-      <c r="N62" s="3">
-        <v>2300</v>
       </c>
       <c r="O62" s="3">
         <v>2300</v>
       </c>
       <c r="P62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="Q62" s="3">
         <v>1600</v>
       </c>
       <c r="R62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S62" s="3">
         <v>2000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2200</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>100</v>
       </c>
       <c r="AC62" s="3">
         <v>100</v>
       </c>
       <c r="AD62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE62" s="3">
         <v>1000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6113,8 +6262,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6220,8 +6372,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6327,115 +6482,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E66" s="3">
         <v>64500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>58500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>67100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>65000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>168000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>78700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>82000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>79700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>75600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>83600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>69300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>78300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>64600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>63500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>50900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>45100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>71300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>61900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>63300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>54200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>55000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>56500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>79100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>81000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6473,8 +6634,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6580,8 +6742,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6687,8 +6852,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6794,8 +6962,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6901,115 +7072,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>440500</v>
+      </c>
+      <c r="E72" s="3">
         <v>436600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>428000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>426600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>421100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>418100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>410900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>409700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>399400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>393100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>471400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>461400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>452900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>438100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>414100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>396800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>367800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>342600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>320900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>392900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>380500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>368200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>362000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>359600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>358600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>350400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>341900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>338800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>329300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>321300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>314700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>309400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>307800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>293400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7115,8 +7292,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7222,8 +7402,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7329,115 +7512,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>321500</v>
+      </c>
+      <c r="E76" s="3">
         <v>319600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>314900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>321500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>332000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>331700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>335300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>333200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>322100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>316700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>398500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>387000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>378000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>363700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>338100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>319100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>288500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>264700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>241300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>311500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>297800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>285500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>277600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>275800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>273900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>264200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>254200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>249400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>238500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>230100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>222500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>227600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>225000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>265900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7543,227 +7732,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E81" s="3">
         <v>10500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>20800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>38100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>44400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>38200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>31700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>15300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>13000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>15200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>14300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>10300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>10200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>20800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7801,16 +7999,17 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3">
         <v>2400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>6500</v>
       </c>
       <c r="F83" s="3">
         <v>6500</v>
@@ -7819,46 +8018,46 @@
         <v>6500</v>
       </c>
       <c r="H83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I83" s="3">
         <v>5300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>6700</v>
       </c>
       <c r="J83" s="3">
         <v>6700</v>
       </c>
       <c r="K83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="L83" s="3">
         <v>6800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>6700</v>
       </c>
       <c r="N83" s="3">
         <v>6700</v>
       </c>
       <c r="O83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P83" s="3">
         <v>6800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>7300</v>
       </c>
       <c r="R83" s="3">
         <v>7300</v>
       </c>
       <c r="S83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="T83" s="3">
         <v>7500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5900</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7200</v>
       </c>
       <c r="V83" s="3">
         <v>7200</v>
@@ -7867,10 +8066,10 @@
         <v>7200</v>
       </c>
       <c r="X83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>6900</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7500</v>
       </c>
       <c r="Z83" s="3">
         <v>7500</v>
@@ -7882,7 +8081,7 @@
         <v>7500</v>
       </c>
       <c r="AC83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="AD83" s="3">
         <v>8200</v>
@@ -7894,22 +8093,25 @@
         <v>8200</v>
       </c>
       <c r="AG83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AH83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>9300</v>
       </c>
       <c r="AI83" s="3">
         <v>9300</v>
       </c>
       <c r="AJ83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AK83" s="3">
         <v>10100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8015,8 +8217,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8122,8 +8327,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8229,8 +8437,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8336,8 +8547,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8443,115 +8657,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E89" s="3">
         <v>20000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>27000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>18800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>55300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>40800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>48400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>61800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>47000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>31100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>40700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-10300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>24200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>14600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>35700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>45300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>42200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>19100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>21000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>19400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8589,115 +8809,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8803,8 +9027,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8910,115 +9137,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>13000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>35500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-48100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-33900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-61500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>102900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-61100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-20200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>12100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-119900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9056,115 +9289,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4100</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>94700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>7500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-7200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-8300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-12000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-15200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-17600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-15100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-12500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-9800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-94800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-6200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AJ96" s="3">
         <v>-7800</v>
       </c>
       <c r="AK96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9270,8 +9507,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9377,8 +9617,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9484,115 +9727,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-97900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-17600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-94800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9620,8 +9869,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9698,111 +9947,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E102" s="3">
         <v>2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-57100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>20500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-20300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-99300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>29000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>39200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>18100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,495 +656,508 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E8" s="3">
         <v>135700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>145800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>122300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>130800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>136800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>130600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>120900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>142800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>149500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>149200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>139400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>140700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>166600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>168000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>178200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>184400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>169300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>145700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>130300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>123600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>105100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>95000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>96300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>114000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>121100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>114900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>128400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>131200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>118200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>104800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>131900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>167400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>161800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E9" s="3">
         <v>105800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>112500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>99600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>101600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>107400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>97900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>96200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>111000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>109700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>100500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>97100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>108500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>104600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>113400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>121300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>111800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>105100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>94600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>90200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>87600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>80400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>75100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>74000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>81400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>87300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>86900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>91800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>95300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>85100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>74600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>96900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>111600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>108400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E10" s="3">
         <v>29900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>33300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>29200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>29400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>32800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>43600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>58100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>63400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>64800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>78800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>72600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>64200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>51100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>40100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>36000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>24700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>32600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>33800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>28000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>36600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>35900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>33100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>30200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>35000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>55800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>53400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1183,19 +1196,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>8200</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1203,11 +1217,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>9800</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1293,8 +1307,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1403,19 +1420,22 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>1600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1423,11 +1443,11 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>500</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1435,8 +1455,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1513,8 +1533,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1522,22 +1545,22 @@
         <v>5600</v>
       </c>
       <c r="E15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F15" s="3">
         <v>5100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>6500</v>
       </c>
       <c r="K15" s="3">
         <v>6500</v>
@@ -1546,7 +1569,7 @@
         <v>6500</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1623,8 +1646,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1660,228 +1686,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E17" s="3">
         <v>127300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>132800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>118500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>121800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>129300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>119800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>114600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>124400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>129500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>119500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>115500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>127800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>123300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>131500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>140400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>132400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>127200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>112800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>106200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>103500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>95300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>89400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>88900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>97600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>104000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>103000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>109000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>112600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>104400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>91500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>116600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>133500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>130200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E18" s="3">
         <v>8500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>44700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>59700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>52000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>17100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>19400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>18600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>13800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>13300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>15300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>33900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>31600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1920,28 +1953,29 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-200</v>
       </c>
       <c r="H20" s="3">
         <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="J20" s="3">
         <v>-400</v>
@@ -1950,198 +1984,204 @@
         <v>-400</v>
       </c>
       <c r="L20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>900</v>
       </c>
       <c r="P20" s="3">
         <v>900</v>
       </c>
       <c r="Q20" s="3">
+        <v>900</v>
+      </c>
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>700</v>
       </c>
       <c r="X20" s="3">
         <v>700</v>
       </c>
       <c r="Y20" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>1000</v>
       </c>
       <c r="AB20" s="3">
         <v>1000</v>
       </c>
       <c r="AC20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>300</v>
       </c>
       <c r="AJ20" s="3">
         <v>300</v>
       </c>
       <c r="AK20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL20" s="3">
         <v>700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E21" s="3">
         <v>14300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>25300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>23800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>27700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>46400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>50100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>55400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>67500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>59900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>48500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>40200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>31900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>28100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>24900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>25000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>20400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>28200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>27100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>22600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>20800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>43500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>42500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2164,35 +2204,35 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
@@ -2200,28 +2240,28 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
@@ -2232,8 +2272,8 @@
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
@@ -2250,228 +2290,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E23" s="3">
         <v>9700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>39500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>45900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>48000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>60300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>52400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>42600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>32900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>17600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>12200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>20000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>18900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>14300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>13400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>15700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>34200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>32400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>12000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>11500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2580,228 +2629,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E26" s="3">
         <v>7800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>38100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>35200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>44400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>38200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>13000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>14300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>9800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>9400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>22200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>20800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E27" s="3">
         <v>7800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>38100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>44400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>38200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>31700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>8200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>13000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>15200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>14300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>9400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>22200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>20800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2910,8 +2968,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2984,8 +3045,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3002,11 +3063,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>500</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3020,8 +3081,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3130,8 +3194,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3240,28 +3307,31 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>200</v>
       </c>
       <c r="H32" s="3">
         <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="J32" s="3">
         <v>400</v>
@@ -3270,198 +3340,204 @@
         <v>400</v>
       </c>
       <c r="L32" s="3">
+        <v>400</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-900</v>
       </c>
       <c r="P32" s="3">
         <v>-900</v>
       </c>
       <c r="Q32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-700</v>
       </c>
       <c r="X32" s="3">
         <v>-700</v>
       </c>
       <c r="Y32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB32" s="3">
         <v>-1000</v>
       </c>
       <c r="AC32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-300</v>
       </c>
       <c r="AJ32" s="3">
         <v>-300</v>
       </c>
       <c r="AK32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E33" s="3">
         <v>7800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>38100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>44400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>38200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>31700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>15300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>13000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>15200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>14300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>9400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>22200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>20800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3570,233 +3646,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E35" s="3">
         <v>7800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>38100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>44400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>38200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>31700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>15300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>13000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>15200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>14300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>9400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>22200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>20800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3835,8 +3920,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3875,201 +3961,205 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E41" s="3">
         <v>16200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>49900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>27700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>29700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>17700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>35400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>22800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>35400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>38500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>137800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>131700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>102700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>63500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>45400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>44000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>35100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>87100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E42" s="3">
         <v>92200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>95500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>88500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>98500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>99500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>102500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>106500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>126200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>122000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>159100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>165300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>165000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>170000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>200000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>165000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>150000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>122000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>121000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>104000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>208900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>149600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>129500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>114500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>99600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>99500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>114300</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>8</v>
@@ -4086,8 +4176,8 @@
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK42" s="3">
         <v>0</v>
@@ -4095,228 +4185,237 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E43" s="3">
         <v>67500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>60200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>65800</v>
-      </c>
-      <c r="I43" s="3">
-        <v>59900</v>
       </c>
       <c r="J43" s="3">
         <v>59900</v>
       </c>
       <c r="K43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="L43" s="3">
         <v>53100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>65200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>65400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>61400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>56200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>69300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>57000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>71900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>76100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>73200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>57900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>58200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>53700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>55800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>52600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>56000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>41500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>52200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>45000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>46800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>50100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>61100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>60100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>53200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>55600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>77600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>69400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E44" s="3">
         <v>70700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>76500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>76000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>73300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>68500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>79300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>69400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>62000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>65000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>61500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>57100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>46900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>43900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>39100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>32000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>28800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>29100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>12100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>28300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>33000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>41500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>36500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>31400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>26200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>24000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>26100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AH44" s="3">
-        <v>52200</v>
       </c>
       <c r="AI44" s="3">
         <v>52200</v>
       </c>
       <c r="AJ44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AK44" s="3">
         <v>55000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>54500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4347,196 +4446,202 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>7100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>12500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>226500</v>
+      </c>
+      <c r="E46" s="3">
         <v>253400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>258400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>247100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>252000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>258600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>271400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>274000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>268100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>264000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>361800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>351000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>334100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>336300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>328700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>308900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>285600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>252200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>234400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>213000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>294900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>264600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>249300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>229900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>220500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>226700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>232200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>214400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>208500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>192900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>166800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>153300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>154200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>170900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>214800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4567,8 +4672,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4645,118 +4750,124 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E48" s="3">
         <v>69300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>74900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>70400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>74300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>72700</v>
       </c>
       <c r="K48" s="3">
         <v>72700</v>
       </c>
       <c r="L48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="M48" s="3">
         <v>75800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>80500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>74000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>77700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>80700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>75300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>66300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>69500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>70800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>72900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>62700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>67900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>73300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>76500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>72100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>74300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>80700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>82700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>84400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>90000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>97100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>103800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>91600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>96600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>102200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>104200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4764,11 +4875,11 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>10100</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -4776,11 +4887,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>10900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -4865,8 +4976,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4975,8 +5089,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5085,118 +5202,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E52" s="3">
         <v>38100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>36600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>36200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>46100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>38300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>44900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43800</v>
-      </c>
-      <c r="T52" s="3">
-        <v>41000</v>
       </c>
       <c r="U52" s="3">
         <v>41000</v>
       </c>
       <c r="V52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="W52" s="3">
         <v>34900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>27000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>24400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>23100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>26500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>26100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>24300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>14300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>13300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>13700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>32600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>33300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>31000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>27900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5305,118 +5428,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>349500</v>
+      </c>
+      <c r="E54" s="3">
         <v>379000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>384000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>373500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>376700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>385000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>398800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>400400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>396900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>389100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>484800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>460900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>443700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>446500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>442300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>420100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>398900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>364100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>348300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>310600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>389900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>362400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>349000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>328500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>320900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>331700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>335500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>316100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>312800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>303300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>284300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>277500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>284100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>304100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>346900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5455,8 +5584,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5495,118 +5625,122 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E57" s="3">
         <v>33400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>32700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>36200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>38100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>37900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>36600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>27100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>39700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>28800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>29300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>24600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>27800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>33000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>30200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>28900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>28200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>32400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>30800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>34600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>45300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>48500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5632,13 +5766,13 @@
         <v>600</v>
       </c>
       <c r="K58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L58" s="3">
         <v>700</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -5715,19 +5849,22 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>300</v>
       </c>
       <c r="G59" s="3">
         <v>300</v>
@@ -5736,240 +5873,246 @@
         <v>300</v>
       </c>
       <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>128100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>29200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>32700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>41000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>42300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>38500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>45100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>40300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>36600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>33700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>31900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>24100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>38200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>31600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>33500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>35900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>20300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>23500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>21800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>33100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>32400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E60" s="3">
         <v>54800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>52000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>50100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>63200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>61600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>163100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>60200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>54500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>66200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>77100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>80400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>77700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>73000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>81800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>67400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>76300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>62500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>61200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>48700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>43000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>55600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>71200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>61800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>62400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>64000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>52700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>54300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>56400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>78400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>80900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -6045,8 +6188,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6066,7 +6212,7 @@
         <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -6078,85 +6224,88 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>5000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>2300</v>
       </c>
       <c r="P62" s="3">
         <v>2300</v>
       </c>
       <c r="Q62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="R62" s="3">
         <v>1600</v>
       </c>
       <c r="S62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T62" s="3">
         <v>2000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2200</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>100</v>
       </c>
       <c r="AD62" s="3">
         <v>100</v>
       </c>
       <c r="AE62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF62" s="3">
         <v>1000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6265,8 +6414,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6375,8 +6527,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6485,118 +6640,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E66" s="3">
         <v>57500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>64500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>58500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>67100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>168000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>62400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>68500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>78700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>82000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>79700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>75600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>83600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>69300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>78300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>64600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>63500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>45100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>71300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>61900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>63300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>64800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>54200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>55000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>56500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>79100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>81000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6635,8 +6796,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6745,8 +6907,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6855,8 +7020,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6965,8 +7133,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7075,118 +7246,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>420300</v>
+      </c>
+      <c r="E72" s="3">
         <v>440500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>436600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>428000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>426600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>421100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>418100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>410900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>409700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>399400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>393100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>471400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>461400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>452900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>438100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>414100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>396800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>367800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>342600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>320900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>392900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>380500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>368200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>362000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>359600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>358600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>350400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>341900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>338800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>329300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>321300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>314700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>309400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>307800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>293400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7295,8 +7472,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7405,8 +7585,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7515,118 +7698,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>289300</v>
+      </c>
+      <c r="E76" s="3">
         <v>321500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>319600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>314900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>321500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>332000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>331700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>335300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>333200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>322100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>316700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>398500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>387000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>378000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>363700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>338100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>319100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>288500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>264700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>241300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>311500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>297800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>285500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>277600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>275800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>273900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>264200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>254200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>249400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>238500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>230100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>222500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>227600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>225000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>265900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7735,233 +7924,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E81" s="3">
         <v>7800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>38100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>44400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>38200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>31700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>15300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>13000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>15200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>14300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>9400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>22200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>20800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8000,19 +8198,20 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E83" s="3">
         <v>5800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>6500</v>
       </c>
       <c r="G83" s="3">
         <v>6500</v>
@@ -8021,46 +8220,46 @@
         <v>6500</v>
       </c>
       <c r="I83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J83" s="3">
         <v>5300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6700</v>
       </c>
       <c r="K83" s="3">
         <v>6700</v>
       </c>
       <c r="L83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="M83" s="3">
         <v>6800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6700</v>
       </c>
       <c r="O83" s="3">
         <v>6700</v>
       </c>
       <c r="P83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>7300</v>
       </c>
       <c r="S83" s="3">
         <v>7300</v>
       </c>
       <c r="T83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="U83" s="3">
         <v>7500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5900</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7200</v>
       </c>
       <c r="W83" s="3">
         <v>7200</v>
@@ -8069,10 +8268,10 @@
         <v>7200</v>
       </c>
       <c r="Y83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>6900</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7500</v>
       </c>
       <c r="AA83" s="3">
         <v>7500</v>
@@ -8084,7 +8283,7 @@
         <v>7500</v>
       </c>
       <c r="AD83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="AE83" s="3">
         <v>8200</v>
@@ -8096,22 +8295,25 @@
         <v>8200</v>
       </c>
       <c r="AH83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AI83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>9300</v>
       </c>
       <c r="AJ83" s="3">
         <v>9300</v>
       </c>
       <c r="AK83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AL83" s="3">
         <v>10100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8220,8 +8422,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8330,8 +8535,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8440,8 +8648,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8550,8 +8761,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8660,118 +8874,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E89" s="3">
         <v>11100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>20000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>13600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>55300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>40800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>48400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>27800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>61800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>47000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>31100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>40700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>24200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>14600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>35700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>45300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>42200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>19100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>18900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>19400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8810,118 +9030,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9030,8 +9254,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9140,118 +9367,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E94" s="3">
         <v>2200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>13000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>35500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-48100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-33900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-61500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>102900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-61100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-24200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>12100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-119900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9290,118 +9523,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E96" s="3">
         <v>4000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>4100</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>94700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>7500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-7200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-8300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-12000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-13900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-17600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-15100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-12500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-9800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-94800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-6200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AK96" s="3">
         <v>-7800</v>
       </c>
       <c r="AL96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9510,8 +9747,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9620,8 +9860,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9730,118 +9973,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-19800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-97900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-17300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-9800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-94800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9872,8 +10121,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9950,114 +10199,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E102" s="3">
         <v>6200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-57100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>11900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-20300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>12600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-99300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>29000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>39200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>18100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,521 +656,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>151100</v>
+      </c>
+      <c r="E8" s="3">
         <v>126800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>132500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>135700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>145800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>122300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>130800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>136800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>130600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>120900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>142800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>149500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>149200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>139400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>140700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>166600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>168000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>178200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>200100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>184400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>169300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>145700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>130300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>123600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>105100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>95000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>96300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>114000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>121100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>114900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>128400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>131200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>118200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>104800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>131900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>167400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>161800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E9" s="3">
         <v>107600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>127300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>105800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>112500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>99600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>101600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>107400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>97900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>96200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>104700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>111000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>109700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>97100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>108500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>104600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>113400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>121300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>111800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>105100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>94600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>90200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>87600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>80400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>75100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>74000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>81400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>87300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>86900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>91800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>95300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>85100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>74600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>96900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>111600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>108400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E10" s="3">
         <v>19200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>33300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>29200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>39500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>43600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>58100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>63400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>64800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>78800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>72600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>64200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>51100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>40100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>36000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>24700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>22300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>32600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>33800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>28000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>36600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>35900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>33100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>30200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>35000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>55800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>53400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1211,13 +1223,14 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>8400</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1225,11 +1238,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>8200</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1237,11 +1250,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>9800</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1327,8 +1340,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1443,13 +1459,16 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>1000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1457,11 +1476,11 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>1600</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1469,11 +1488,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>500</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1481,8 +1500,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1559,13 +1578,16 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5600</v>
+        <v>6200</v>
       </c>
       <c r="E15" s="3">
         <v>5600</v>
@@ -1574,22 +1596,22 @@
         <v>5600</v>
       </c>
       <c r="G15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H15" s="3">
         <v>5100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>6500</v>
       </c>
       <c r="M15" s="3">
         <v>6500</v>
@@ -1598,7 +1620,7 @@
         <v>6500</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1675,8 +1697,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1714,240 +1739,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E17" s="3">
         <v>130300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>153200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>127300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>132800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>118500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>121800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>129300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>119800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>114600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>124400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>132400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>129500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>119500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>115500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>127800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>123300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>131500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>140400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>132400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>127200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>112800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>106200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>103500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>95300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>89400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>88900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>97600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>104000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>103000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>109000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>112600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>104400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>91500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>116600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>133500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>130200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>38800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>44700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>46700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>59700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>52000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>42100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>19400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>18600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>13300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>15300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>33900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>31600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1988,34 +2020,35 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-200</v>
       </c>
       <c r="J20" s="3">
         <v>-200</v>
       </c>
       <c r="K20" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="L20" s="3">
         <v>-400</v>
@@ -2024,204 +2057,210 @@
         <v>-400</v>
       </c>
       <c r="N20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>900</v>
       </c>
       <c r="R20" s="3">
         <v>900</v>
       </c>
       <c r="S20" s="3">
+        <v>900</v>
+      </c>
+      <c r="T20" s="3">
         <v>1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>700</v>
       </c>
       <c r="Z20" s="3">
         <v>700</v>
       </c>
       <c r="AA20" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>900</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>1000</v>
       </c>
       <c r="AD20" s="3">
         <v>1000</v>
       </c>
       <c r="AE20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>100</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>300</v>
       </c>
       <c r="AL20" s="3">
         <v>300</v>
       </c>
       <c r="AM20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN20" s="3">
         <v>700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E21" s="3">
         <v>2900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-14700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>18700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>14500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>25300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>23800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>27400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>32800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>46400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>50100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>55400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>67500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>59900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>48500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>40200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>31900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>17800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>13900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>15900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>24900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>25000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>20400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>28200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>27100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>22600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>20800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>25000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>43500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>42500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2250,35 +2289,35 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
@@ -2286,28 +2325,28 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
       <c r="AA22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
       </c>
       <c r="AC22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>8</v>
@@ -2318,8 +2357,8 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
@@ -2336,240 +2375,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>39500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>45900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>48000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>60300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>52400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>42600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>32900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>17400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>12200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>20000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>18900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>13400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>15700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>34200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>32400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>4100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>12000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>11500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2684,240 +2732,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>38100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>44400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>38200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>31700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>13000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>9200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>14300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>9400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>10200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>22200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>20800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>38100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>44400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>38200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>31700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>13000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>15200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>14300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>10200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>22200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>20800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3032,8 +3089,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3112,8 +3172,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3130,11 +3190,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>500</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3148,8 +3208,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3264,8 +3327,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3380,34 +3446,37 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>200</v>
       </c>
       <c r="J32" s="3">
         <v>200</v>
       </c>
       <c r="K32" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L32" s="3">
         <v>400</v>
@@ -3416,204 +3485,210 @@
         <v>400</v>
       </c>
       <c r="N32" s="3">
+        <v>400</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-900</v>
       </c>
       <c r="R32" s="3">
         <v>-900</v>
       </c>
       <c r="S32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-700</v>
       </c>
       <c r="Z32" s="3">
         <v>-700</v>
       </c>
       <c r="AA32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-900</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AD32" s="3">
         <v>-1000</v>
       </c>
       <c r="AE32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>-300</v>
       </c>
       <c r="AL32" s="3">
         <v>-300</v>
       </c>
       <c r="AM32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AN32" s="3">
         <v>-700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>20800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>30200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>38100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>44400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>38200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>31700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>15300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>13000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>15200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>14300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>9400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>10200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>22200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>20800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3728,245 +3803,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>20800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>30200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>38100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>44400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>38200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>31700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>15300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>13000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>15200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>14300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>9400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>10200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>22200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>20800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4007,8 +4091,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4049,213 +4134,217 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E41" s="3">
         <v>16100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>65200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>23600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>20100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>29700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>38000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>35400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>22800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>35400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>38500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>137800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>131700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>102700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>63500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>45400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>44000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>35100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>87100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E42" s="3">
         <v>64800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>78100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>95500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>88500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>99500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>102500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>106500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>126200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>122000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>159100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>165300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>165000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>170000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>200000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>165000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>150000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>122000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>121000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>104000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>208900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>149600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>129500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>114500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>99600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>99500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>114300</v>
-      </c>
-      <c r="AF42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>8</v>
@@ -4272,8 +4361,8 @@
       <c r="AK42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL42" s="3">
-        <v>0</v>
+      <c r="AL42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AM42" s="3">
         <v>0</v>
@@ -4281,240 +4370,249 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>64500</v>
+      </c>
+      <c r="E43" s="3">
         <v>59900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>61800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>67500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>67100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>60200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>65800</v>
-      </c>
-      <c r="K43" s="3">
-        <v>59900</v>
       </c>
       <c r="L43" s="3">
         <v>59900</v>
       </c>
       <c r="M43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="N43" s="3">
         <v>53100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>65200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>65400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>61400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>56200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>69300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>57000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>71900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>76100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>73200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>57900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>58200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>53700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>55800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>52600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>56000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>41500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>52200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>45000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>46800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>50100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>61100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>53200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>55600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>77600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>69400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E44" s="3">
         <v>54600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>53000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>70700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>76500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>76000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>73300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>68500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>79800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>69400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>62000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>65000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>61500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>57100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>46900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>43900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>39100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>32000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>28800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>29100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>12100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>28300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>33000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>41500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>36500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>31400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>26200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>24000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>26100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AJ44" s="3">
-        <v>52200</v>
       </c>
       <c r="AK44" s="3">
         <v>52200</v>
       </c>
       <c r="AL44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AM44" s="3">
         <v>55000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>54500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4551,202 +4649,208 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>7100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>12500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E46" s="3">
         <v>208300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>226500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>253400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>258400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>247100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>252000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>258600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>271400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>274000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>268100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>264000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>361800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>351000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>334100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>336300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>328700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>308900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>285600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>252200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>234400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>213000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>294900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>264600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>249300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>229900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>220500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>226700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>232200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>214400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>208500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>192900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>166800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>153300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>154200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>170900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>214800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4783,8 +4887,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4861,129 +4965,135 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E48" s="3">
         <v>84800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>69400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>70400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>74300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>72700</v>
       </c>
       <c r="M48" s="3">
         <v>72700</v>
       </c>
       <c r="N48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="O48" s="3">
         <v>75800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>80500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>74000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>77700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>80700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>75300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>66300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>69500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>70800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>72900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>62700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>67900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>73300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>76500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>72100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>74300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>80700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>82700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>84400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>90000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>97100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>103800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>91600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>96600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>102200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>104200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4992,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>10100</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -5004,11 +5114,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>10900</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -5093,8 +5203,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5209,8 +5322,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5325,124 +5441,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E52" s="3">
         <v>29200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38100</v>
       </c>
-      <c r="G52" s="3">
-        <v>25300</v>
-      </c>
       <c r="H52" s="3">
+        <v>25800</v>
+      </c>
+      <c r="I52" s="3">
         <v>36600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>36200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>46100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>38300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>44900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43800</v>
-      </c>
-      <c r="V52" s="3">
-        <v>41000</v>
       </c>
       <c r="W52" s="3">
         <v>41000</v>
       </c>
       <c r="X52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Y52" s="3">
         <v>34900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>27000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>24400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>23100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>26500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>26100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>24300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>17200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>14300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>13300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>13700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>32600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>33300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>31000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>27900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5557,124 +5679,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E54" s="3">
         <v>342300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>349500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>379000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>384000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>373500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>376700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>385000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>398800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>400400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>396900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>389100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>484800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>460900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>443700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>446500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>442300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>420100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>398900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>364100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>348300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>310600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>389900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>362400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>349000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>328500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>320900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>331700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>335500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>316100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>312800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>303300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>284300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>277500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>284100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>304100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>346900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5715,8 +5843,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5757,124 +5886,128 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E57" s="3">
         <v>32400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33400</v>
       </c>
-      <c r="G57" s="3">
-        <v>13200</v>
-      </c>
       <c r="H57" s="3">
+        <v>22000</v>
+      </c>
+      <c r="I57" s="3">
         <v>30900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>32700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>31000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>38100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>37900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>34500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>36600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>27100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>39700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>28800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>29300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>24600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>21900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>27800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>33000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>30200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>28900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>28200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>30800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>34600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>45300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>48500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5906,13 +6039,13 @@
         <v>600</v>
       </c>
       <c r="M58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N58" s="3">
         <v>700</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -5989,25 +6122,28 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>300</v>
       </c>
       <c r="I59" s="3">
         <v>300</v>
@@ -6016,252 +6152,258 @@
         <v>300</v>
       </c>
       <c r="K59" s="3">
+        <v>300</v>
+      </c>
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>128100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>32700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>41000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>42300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>39800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>38500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>45100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>40300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>36600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>31900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>24100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>21000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>27700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>38200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>31600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>33500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>35900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>20300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>23500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>21800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>33100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>32400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E60" s="3">
         <v>58900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>57200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>60800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>63200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>61200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>163100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>60200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>54500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>66200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>77100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>80400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>77700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>73000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>81800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>67400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>76300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>62500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>61200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>48700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>43000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>55600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>71200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>61800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>62400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>64000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>52700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>54300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>56400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>78400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>80900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -6337,8 +6479,11 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6364,7 +6509,7 @@
         <v>100</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -6376,85 +6521,88 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>5000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>2300</v>
       </c>
       <c r="R62" s="3">
         <v>2300</v>
       </c>
       <c r="S62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="T62" s="3">
         <v>1600</v>
       </c>
       <c r="U62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V62" s="3">
         <v>2000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2200</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>100</v>
       </c>
       <c r="AF62" s="3">
         <v>100</v>
       </c>
       <c r="AG62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH62" s="3">
         <v>1000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6569,8 +6717,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6685,8 +6836,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6801,124 +6955,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E66" s="3">
         <v>62700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>64500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>58500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>63700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>168000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>62400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>78700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>82000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>79700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>75600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>83600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>69300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>78300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>64600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>63500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>50900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>45100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>57800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>71300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>61900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>63300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>64800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>54200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>55000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>56500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>79100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>81000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6959,8 +7119,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7075,8 +7236,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7191,8 +7355,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7307,8 +7474,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7423,124 +7593,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>422000</v>
+      </c>
+      <c r="E72" s="3">
         <v>419200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>420300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>440500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>436600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>428000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>426600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>421100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>418100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>410900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>409700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>399400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>393100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>471400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>461400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>452900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>438100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>414100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>396800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>367800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>342600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>320900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>392900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>380500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>368200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>362000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>359600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>358600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>350400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>341900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>338800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>329300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>321300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>314700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>309400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>307800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>293400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7655,8 +7831,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7771,8 +7950,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7887,124 +8069,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>283800</v>
+      </c>
+      <c r="E76" s="3">
         <v>279600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>289300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>321500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>319600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>314900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>321500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>332000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>331700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>335300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>333200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>322100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>316700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>398500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>387000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>378000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>363700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>338100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>319100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>288500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>264700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>241300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>311500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>297800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>285500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>277600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>275800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>273900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>264200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>254200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>249400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>238500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>230100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>222500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>227600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>225000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>265900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8119,245 +8307,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>20800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>30200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>38100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>44400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>38200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>31700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>15300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>13000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>15200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>14300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>9400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>10200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>22200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>20800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8398,25 +8595,26 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E83" s="3">
         <v>5800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>6500</v>
       </c>
       <c r="I83" s="3">
         <v>6500</v>
@@ -8425,46 +8623,46 @@
         <v>6500</v>
       </c>
       <c r="K83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="L83" s="3">
         <v>5300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6700</v>
       </c>
       <c r="M83" s="3">
         <v>6700</v>
       </c>
       <c r="N83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="O83" s="3">
         <v>6800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>6700</v>
       </c>
       <c r="Q83" s="3">
         <v>6700</v>
       </c>
       <c r="R83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="S83" s="3">
         <v>6800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7300</v>
       </c>
       <c r="U83" s="3">
         <v>7300</v>
       </c>
       <c r="V83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="W83" s="3">
         <v>7500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5900</v>
-      </c>
-      <c r="X83" s="3">
-        <v>7200</v>
       </c>
       <c r="Y83" s="3">
         <v>7200</v>
@@ -8473,10 +8671,10 @@
         <v>7200</v>
       </c>
       <c r="AA83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AB83" s="3">
         <v>6900</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>7500</v>
       </c>
       <c r="AC83" s="3">
         <v>7500</v>
@@ -8488,7 +8686,7 @@
         <v>7500</v>
       </c>
       <c r="AF83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="AG83" s="3">
         <v>8200</v>
@@ -8500,22 +8698,25 @@
         <v>8200</v>
       </c>
       <c r="AJ83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AK83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>9300</v>
       </c>
       <c r="AL83" s="3">
         <v>9300</v>
       </c>
       <c r="AM83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AN83" s="3">
         <v>10100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8630,8 +8831,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8746,8 +8950,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8862,8 +9069,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8978,8 +9188,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9094,124 +9307,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E89" s="3">
         <v>12900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>55300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>40800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>27800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>61800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>47000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>31100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>15400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-10300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>24200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>14600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>35700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>45300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>42200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>19100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>21000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>18900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>19400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9252,124 +9471,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-16200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9484,8 +9707,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9600,124 +9826,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>8500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>13000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>35500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>19100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-48100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-33900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-61500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>102900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-61100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-20200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>12100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-119900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9758,124 +9990,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>600</v>
+      </c>
+      <c r="E96" s="3">
         <v>2600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4100</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>94700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>5700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>7500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-7200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-12000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-15200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-13900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-17600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-15100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-12500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-9800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-94800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AM96" s="3">
         <v>-7800</v>
       </c>
       <c r="AN96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9990,8 +10226,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10106,8 +10345,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10222,124 +10464,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-19800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-97900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-17600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-17300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-94800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10376,8 +10624,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10454,120 +10702,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-57100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-99300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>29000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>39200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>8900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>RGR</t>
   </si>
@@ -656,533 +656,546 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>141400</v>
+      </c>
+      <c r="E8" s="3">
         <v>151100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>126800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>132500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>135700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>145800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>122300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>130800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>136800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>130600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>120900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>142800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>149500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>149200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>139400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>140700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>166600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>168000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>178200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>200100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>184400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>169300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>145700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>130300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>123600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>105100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>95000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>96300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>114000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>121100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>114900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>128400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>131200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>118200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>104800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>131900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>167400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>161800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E9" s="3">
         <v>123300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>107600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>127300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>105800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>112500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>101600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>107400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>97900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>96200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>111000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>109700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>97100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>108500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>104600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>113400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>121300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>111800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>105100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>94600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>90200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>87600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>80400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>75100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>74000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>81400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>87300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>86900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>91800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>95300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>85100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>74600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>96900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>111600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>108400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E10" s="3">
         <v>27800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>29900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>33300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>32800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>43600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>58100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>63400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>64800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>78800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>72600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>64200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>51100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>40100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>36000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>22300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>32600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>33800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>28000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>36600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>35900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>33100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>30200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>35000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>55800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>53400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1224,16 +1237,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>8400</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1241,11 +1255,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>8200</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1253,11 +1267,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>9800</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1343,8 +1357,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1462,16 +1479,19 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1479,11 +1499,11 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1491,11 +1511,11 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>500</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1503,8 +1523,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1581,16 +1601,19 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E15" s="3">
         <v>6200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5600</v>
       </c>
       <c r="F15" s="3">
         <v>5600</v>
@@ -1599,22 +1622,22 @@
         <v>5600</v>
       </c>
       <c r="H15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I15" s="3">
         <v>5100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>6500</v>
       </c>
       <c r="N15" s="3">
         <v>6500</v>
@@ -1623,7 +1646,7 @@
         <v>6500</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1700,8 +1723,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,246 +1766,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E17" s="3">
         <v>146600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>130300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>153200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>127300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>132800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>118500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>121800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>129300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>119800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>114600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>124400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>129500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>119500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>115500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>127800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>123300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>131500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>140400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>132400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>127200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>112800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>106200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>103500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>95300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>89400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>88900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>97600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>104000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>103000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>109000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>112600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>104400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>91500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>116600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>133500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>130200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-20700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>25200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>38800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>44700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>46700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>59700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>52000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>42100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>19400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>18600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>13800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>13300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>15300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>33900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>31600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2021,37 +2054,38 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
       </c>
       <c r="L20" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="M20" s="3">
         <v>-400</v>
@@ -2060,207 +2094,213 @@
         <v>-400</v>
       </c>
       <c r="O20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>900</v>
       </c>
       <c r="S20" s="3">
         <v>900</v>
       </c>
       <c r="T20" s="3">
+        <v>900</v>
+      </c>
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>700</v>
       </c>
       <c r="AA20" s="3">
         <v>700</v>
       </c>
       <c r="AB20" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>900</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1000</v>
       </c>
       <c r="AE20" s="3">
         <v>1000</v>
       </c>
       <c r="AF20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>100</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>300</v>
       </c>
       <c r="AM20" s="3">
         <v>300</v>
       </c>
       <c r="AN20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AO20" s="3">
         <v>700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>11100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>25300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>23800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>32800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>46400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>50100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>55400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>67500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>59900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>48500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>40200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>31900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>28100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>17800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>13900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>15900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>25000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>20400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>28200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>27100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>22600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>20800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>25000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>43500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>42500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2292,35 +2332,35 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
@@ -2328,28 +2368,28 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
       <c r="AB22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
       </c>
       <c r="AD22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
+      <c r="AF22" s="3">
+        <v>0</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>8</v>
@@ -2360,8 +2400,8 @@
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
@@ -2378,246 +2418,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
         <v>4600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>39500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>45900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>48000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>60300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>52400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>42600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>32900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>12200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>20000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>14300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>13400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>15700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>34200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>32400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>15900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>4500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>4100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>5500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>12000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>11500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2735,246 +2784,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>38100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>35200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>44400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>38200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>24800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>13000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>12300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>9200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>9800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>9400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>10200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>22200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>20800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>38100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>44400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>38200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>31700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>13000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>12300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>15200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>9400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>10200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>22200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>20800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3092,8 +3150,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3175,8 +3236,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3193,11 +3254,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>500</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3211,8 +3272,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3330,8 +3394,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3449,37 +3516,40 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
       </c>
       <c r="L32" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M32" s="3">
         <v>400</v>
@@ -3488,207 +3558,213 @@
         <v>400</v>
       </c>
       <c r="O32" s="3">
+        <v>400</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-900</v>
       </c>
       <c r="S32" s="3">
         <v>-900</v>
       </c>
       <c r="T32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-700</v>
       </c>
       <c r="AA32" s="3">
         <v>-700</v>
       </c>
       <c r="AB32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-900</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AE32" s="3">
         <v>-1000</v>
       </c>
       <c r="AF32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AL32" s="3">
-        <v>-300</v>
       </c>
       <c r="AM32" s="3">
         <v>-300</v>
       </c>
       <c r="AN32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AO32" s="3">
         <v>-700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>20800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>38100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>44400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>38200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>31700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>15300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>13000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>15200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>10300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>9400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>10200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>22200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>20800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3806,251 +3882,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>20800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>38100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>44400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>38200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>31700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>15300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>13000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>15200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>10300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>9400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>10200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>22200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>20800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4092,8 +4177,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4135,219 +4221,223 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E41" s="3">
         <v>18500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>49900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>27700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>23600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>17700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>35400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>22800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>32200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>35400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>38500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>137800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>131700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>102700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>63500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>45400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>44000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>35100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>87100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>81400</v>
+      </c>
+      <c r="E42" s="3">
         <v>74100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>64800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>78100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>95500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>88500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>98500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>99500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>102500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>106500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>126200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>122000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>159100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>165300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>165000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>170000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>200000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>165000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>150000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>122000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>121000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>104000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>208900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>149600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>129500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>114500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>99600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>99500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>114300</v>
-      </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>8</v>
@@ -4364,8 +4454,8 @@
       <c r="AL42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM42" s="3">
-        <v>0</v>
+      <c r="AM42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AN42" s="3">
         <v>0</v>
@@ -4373,246 +4463,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E43" s="3">
         <v>64500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>59900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>67500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>67100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>60200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>65800</v>
-      </c>
-      <c r="L43" s="3">
-        <v>59900</v>
       </c>
       <c r="M43" s="3">
         <v>59900</v>
       </c>
       <c r="N43" s="3">
+        <v>59900</v>
+      </c>
+      <c r="O43" s="3">
         <v>53100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>65200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>65400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>61400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>56200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>69300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>57000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>71900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>76100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>73200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>57900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>58200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>53700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>55800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>52600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>56000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>41500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>52200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>45000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>46800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>50100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>61100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>60100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>53200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>55600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>77600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>69400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E44" s="3">
         <v>42900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>54600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>53000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>70700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>76500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>76000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>73300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>68500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>79300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>62000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>65000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>57100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>46900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>43900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>39100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>32000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>28800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>29100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>12100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>28300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>33000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>41500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>36500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>31400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>26200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>24000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>26100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>39700</v>
-      </c>
-      <c r="AK44" s="3">
-        <v>52200</v>
       </c>
       <c r="AL44" s="3">
         <v>52200</v>
       </c>
       <c r="AM44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="AN44" s="3">
         <v>55000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>54500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4652,205 +4751,211 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>12500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E46" s="3">
         <v>211600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>208300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>226500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>253400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>258400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>247100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>252000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>258600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>271400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>274000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>268100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>264000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>361800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>351000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>334100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>336300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>328700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>308900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>285600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>252200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>234400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>213000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>294900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>264600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>249300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>229900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>220500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>226700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>232200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>214400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>208500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>192900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>166800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>153300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>154200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>170900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>214800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>231100</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4890,8 +4995,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4968,136 +5073,142 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E48" s="3">
         <v>81900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>84800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>69300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>74900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>70400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>74300</v>
-      </c>
-      <c r="M48" s="3">
-        <v>72700</v>
       </c>
       <c r="N48" s="3">
         <v>72700</v>
       </c>
       <c r="O48" s="3">
+        <v>72700</v>
+      </c>
+      <c r="P48" s="3">
         <v>75800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>80500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>74000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>77700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>80700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>75300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>66300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>69500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>70800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>72900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>62700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>67900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>73300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>76500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>72100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>74300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>80700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>82700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>84400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>90000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>97100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>103800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>91600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>96600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>102200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>104200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>8800</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -5105,11 +5216,11 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>9600</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -5117,11 +5228,11 @@
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>10900</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
@@ -5206,8 +5317,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5325,8 +5439,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5444,127 +5561,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E52" s="3">
         <v>20000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>36600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>36200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>35800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>38300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>44900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43800</v>
-      </c>
-      <c r="W52" s="3">
-        <v>41000</v>
       </c>
       <c r="X52" s="3">
         <v>41000</v>
       </c>
       <c r="Y52" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Z52" s="3">
         <v>34900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>27000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>24400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>23100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>26500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>26100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>17200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>14300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>13700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>32600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>33300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>31000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>27900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5682,127 +5805,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>349100</v>
+      </c>
+      <c r="E54" s="3">
         <v>342000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>342300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>349500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>379000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>384000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>373500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>376700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>385000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>398800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>400400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>396900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>389100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>484800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>460900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>443700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>446500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>442300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>420100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>398900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>364100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>348300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>310600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>389900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>362400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>349000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>328500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>320900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>331700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>335500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>316100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>312800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>303300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>284300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>277500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>284100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>304100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>346900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5844,8 +5973,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5887,127 +6017,131 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E57" s="3">
         <v>19600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>32700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>31000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>38100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>37900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>36600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>27100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>39700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>28800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>29300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>24600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>21900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>27800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>33000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>30200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>28900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>28200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>32400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>30800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>34600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>45300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>48500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6042,13 +6176,13 @@
         <v>600</v>
       </c>
       <c r="N58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O58" s="3">
         <v>700</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -6125,28 +6259,31 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>300</v>
       </c>
       <c r="J59" s="3">
         <v>300</v>
@@ -6155,258 +6292,264 @@
         <v>300</v>
       </c>
       <c r="L59" s="3">
+        <v>300</v>
+      </c>
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>128100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>29200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>32700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>41000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>42300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>39800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>38500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>45100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>40300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>36600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>33700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>31900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>24100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>21000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>27700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>38200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>31600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>33500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>35900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>20300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>23500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>21800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>33100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>32400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>31800</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E60" s="3">
         <v>54700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>57200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>60800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>50100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>63200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>61200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>59900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>61600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>163100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>60200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>54500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>66200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>77100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>80400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>77700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>73000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>81800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>67400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>76300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>62500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>61200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>48700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>43000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>55600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>71200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>61800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>62400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>52700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>54300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>56400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>78400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>80900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>85200</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6482,8 +6625,11 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6512,7 +6658,7 @@
         <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -6524,85 +6670,88 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>5000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2200</v>
-      </c>
-      <c r="R62" s="3">
-        <v>2300</v>
       </c>
       <c r="S62" s="3">
         <v>2300</v>
       </c>
       <c r="T62" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="U62" s="3">
         <v>1600</v>
       </c>
       <c r="V62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W62" s="3">
         <v>2000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2200</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>100</v>
       </c>
       <c r="AG62" s="3">
         <v>100</v>
       </c>
       <c r="AH62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI62" s="3">
         <v>1000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6720,8 +6869,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6839,8 +6991,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6958,127 +7113,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E66" s="3">
         <v>58200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>62700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>64500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>65000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>63700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>168000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>62400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>68500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>78700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>82000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>79700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>75600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>83600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>69300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>78300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>64600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>63500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>50900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>45100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>57800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>71300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>61900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>63300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>64800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>54200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>55000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>56500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>79100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>81000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>94700</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7120,8 +7281,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7239,8 +7401,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7358,8 +7523,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7477,8 +7645,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7596,127 +7767,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>420900</v>
+      </c>
+      <c r="E72" s="3">
         <v>422000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>419200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>420300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>440500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>436600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>428000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>426600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>421100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>418100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>410900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>409700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>399400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>393100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>471400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>461400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>452900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>438100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>414100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>396800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>367800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>342600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>320900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>392900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>380500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>368200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>362000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>359600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>358600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>350400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>341900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>338800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>329300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>321300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>314700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>309400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>307800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>293400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>280400</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7834,8 +8011,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7953,8 +8133,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8072,127 +8255,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>283300</v>
+      </c>
+      <c r="E76" s="3">
         <v>283800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>279600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>289300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>321500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>319600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>314900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>321500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>332000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>331700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>335300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>333200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>322100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>316700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>398500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>387000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>378000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>363700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>338100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>319100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>288500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>264700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>241300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>311500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>297800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>285500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>277600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>275800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>273900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>264200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>254200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>249400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>238500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>230100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>222500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>227600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>225000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>265900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>266100</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8310,251 +8499,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>20800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>38100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>44400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>38200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>31700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>15300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>13000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>15200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>10300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>9400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>10200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>22200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>20800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8596,28 +8794,29 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E83" s="3">
         <v>4600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>6500</v>
       </c>
       <c r="J83" s="3">
         <v>6500</v>
@@ -8626,46 +8825,46 @@
         <v>6500</v>
       </c>
       <c r="L83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="M83" s="3">
         <v>5300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>6700</v>
       </c>
       <c r="N83" s="3">
         <v>6700</v>
       </c>
       <c r="O83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P83" s="3">
         <v>6800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5700</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>6700</v>
       </c>
       <c r="R83" s="3">
         <v>6700</v>
       </c>
       <c r="S83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="T83" s="3">
         <v>6800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7300</v>
       </c>
       <c r="V83" s="3">
         <v>7300</v>
       </c>
       <c r="W83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="X83" s="3">
         <v>7500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5900</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7200</v>
       </c>
       <c r="Z83" s="3">
         <v>7200</v>
@@ -8674,10 +8873,10 @@
         <v>7200</v>
       </c>
       <c r="AB83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AC83" s="3">
         <v>6900</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>7500</v>
       </c>
       <c r="AD83" s="3">
         <v>7500</v>
@@ -8689,7 +8888,7 @@
         <v>7500</v>
       </c>
       <c r="AG83" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="AH83" s="3">
         <v>8200</v>
@@ -8701,22 +8900,25 @@
         <v>8200</v>
       </c>
       <c r="AK83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AL83" s="3">
         <v>7400</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>9300</v>
       </c>
       <c r="AM83" s="3">
         <v>9300</v>
       </c>
       <c r="AN83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="AO83" s="3">
         <v>10100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8834,8 +9036,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8953,8 +9158,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9072,8 +9280,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9191,8 +9402,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9310,127 +9524,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E89" s="3">
         <v>15500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>55300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>40800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>27800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>61800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>47000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>31100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>40700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>24200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>14600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>35700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>45300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>42200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>19100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>21000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>18900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>19400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9472,127 +9692,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9710,8 +9934,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9829,127 +10056,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>8500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>13000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>35500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>19100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-48100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-33900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-61500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>102900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-61100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-20200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>12100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-119900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-11800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-11700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9991,127 +10224,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E96" s="3">
         <v>600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>4100</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>94700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>5700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>7500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-8300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-12000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-15200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-13900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-17600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-15100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-12500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-94800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-8500</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-7800</v>
       </c>
       <c r="AN96" s="3">
         <v>-7800</v>
       </c>
       <c r="AO96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10229,8 +10466,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10348,8 +10588,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10467,127 +10710,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-19800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-97900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-13900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-17600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-17300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-94800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-15400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-8500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-63700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-9300</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10627,8 +10876,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10705,123 +10954,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-57100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>20500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-99300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>29000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>39200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>18100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>8900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-52000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-14200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1700</v>
       </c>
     </row>
